--- a/eval/cases/branch-lookup-50/next.output.xlsx
+++ b/eval/cases/branch-lookup-50/next.output.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="413">
   <si>
     <t>Sale ID</t>
   </si>
@@ -40,39 +40,42 @@
     <t>Helena</t>
   </si>
   <si>
+    <t>Shelves</t>
+  </si>
+  <si>
+    <t>S-05002</t>
+  </si>
+  <si>
+    <t>B30</t>
+  </si>
+  <si>
+    <t>Phoenix</t>
+  </si>
+  <si>
+    <t>S-05003</t>
+  </si>
+  <si>
+    <t>B36</t>
+  </si>
+  <si>
+    <t>Memphis</t>
+  </si>
+  <si>
+    <t>Lamps</t>
+  </si>
+  <si>
+    <t>S-05004</t>
+  </si>
+  <si>
+    <t>B44</t>
+  </si>
+  <si>
+    <t>Fresno</t>
+  </si>
+  <si>
     <t>Cabinets</t>
   </si>
   <si>
-    <t>S-05002</t>
-  </si>
-  <si>
-    <t>B30</t>
-  </si>
-  <si>
-    <t>Phoenix</t>
-  </si>
-  <si>
-    <t>S-05003</t>
-  </si>
-  <si>
-    <t>B36</t>
-  </si>
-  <si>
-    <t>Memphis</t>
-  </si>
-  <si>
-    <t>Lamps</t>
-  </si>
-  <si>
-    <t>S-05004</t>
-  </si>
-  <si>
-    <t>B44</t>
-  </si>
-  <si>
-    <t>Fresno</t>
-  </si>
-  <si>
     <t>S-05005</t>
   </si>
   <si>
@@ -94,33 +97,33 @@
     <t>Provo</t>
   </si>
   <si>
+    <t>Chairs</t>
+  </si>
+  <si>
+    <t>S-05007</t>
+  </si>
+  <si>
+    <t>S-05008</t>
+  </si>
+  <si>
+    <t>B33</t>
+  </si>
+  <si>
+    <t>Portland</t>
+  </si>
+  <si>
+    <t>S-05009</t>
+  </si>
+  <si>
+    <t>B49</t>
+  </si>
+  <si>
+    <t>Garland</t>
+  </si>
+  <si>
     <t>Desks</t>
   </si>
   <si>
-    <t>S-05007</t>
-  </si>
-  <si>
-    <t>S-05008</t>
-  </si>
-  <si>
-    <t>B33</t>
-  </si>
-  <si>
-    <t>Portland</t>
-  </si>
-  <si>
-    <t>Chairs</t>
-  </si>
-  <si>
-    <t>S-05009</t>
-  </si>
-  <si>
-    <t>B49</t>
-  </si>
-  <si>
-    <t>Garland</t>
-  </si>
-  <si>
     <t>S-05010</t>
   </si>
   <si>
@@ -145,979 +148,979 @@
     <t>Seattle</t>
   </si>
   <si>
-    <t>Shelves</t>
-  </si>
-  <si>
     <t>S-05014</t>
   </si>
   <si>
     <t>B14</t>
   </si>
   <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>S-05015</t>
+  </si>
+  <si>
+    <t>B21</t>
+  </si>
+  <si>
+    <t>Dover</t>
+  </si>
+  <si>
+    <t>S-05016</t>
+  </si>
+  <si>
+    <t>B01</t>
+  </si>
+  <si>
+    <t>Tulsa</t>
+  </si>
+  <si>
+    <t>S-05017</t>
+  </si>
+  <si>
+    <t>B15</t>
+  </si>
+  <si>
+    <t>Laredo</t>
+  </si>
+  <si>
+    <t>S-05018</t>
+  </si>
+  <si>
+    <t>B41</t>
+  </si>
+  <si>
+    <t>Hartford</t>
+  </si>
+  <si>
+    <t>S-05019</t>
+  </si>
+  <si>
+    <t>S-05020</t>
+  </si>
+  <si>
+    <t>B07</t>
+  </si>
+  <si>
+    <t>S-05021</t>
+  </si>
+  <si>
+    <t>B42</t>
+  </si>
+  <si>
+    <t>Wichita</t>
+  </si>
+  <si>
+    <t>S-05022</t>
+  </si>
+  <si>
+    <t>S-05023</t>
+  </si>
+  <si>
+    <t>S-05024</t>
+  </si>
+  <si>
+    <t>B50</t>
+  </si>
+  <si>
+    <t>Irvine</t>
+  </si>
+  <si>
+    <t>S-05025</t>
+  </si>
+  <si>
+    <t>S-05026</t>
+  </si>
+  <si>
+    <t>B38</t>
+  </si>
+  <si>
+    <t>Raleigh</t>
+  </si>
+  <si>
+    <t>S-05027</t>
+  </si>
+  <si>
+    <t>B06</t>
+  </si>
+  <si>
+    <t>Macon</t>
+  </si>
+  <si>
+    <t>S-05028</t>
+  </si>
+  <si>
+    <t>B10</t>
+  </si>
+  <si>
+    <t>Dayton</t>
+  </si>
+  <si>
+    <t>S-05029</t>
+  </si>
+  <si>
+    <t>B31</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>S-05030</t>
+  </si>
+  <si>
+    <t>B27</t>
+  </si>
+  <si>
+    <t>Miami</t>
+  </si>
+  <si>
+    <t>S-05031</t>
+  </si>
+  <si>
+    <t>S-05032</t>
+  </si>
+  <si>
+    <t>B19</t>
+  </si>
+  <si>
+    <t>Madison</t>
+  </si>
+  <si>
+    <t>S-05033</t>
+  </si>
+  <si>
+    <t>S-05034</t>
+  </si>
+  <si>
+    <t>B29</t>
+  </si>
+  <si>
+    <t>S-05035</t>
+  </si>
+  <si>
+    <t>B35</t>
+  </si>
+  <si>
+    <t>Detroit</t>
+  </si>
+  <si>
+    <t>S-05036</t>
+  </si>
+  <si>
+    <t>S-05037</t>
+  </si>
+  <si>
+    <t>S-05038</t>
+  </si>
+  <si>
+    <t>B46</t>
+  </si>
+  <si>
+    <t>Anaheim</t>
+  </si>
+  <si>
+    <t>S-05039</t>
+  </si>
+  <si>
+    <t>B11</t>
+  </si>
+  <si>
+    <t>S-05040</t>
+  </si>
+  <si>
+    <t>B12</t>
+  </si>
+  <si>
+    <t>Albany</t>
+  </si>
+  <si>
+    <t>S-05041</t>
+  </si>
+  <si>
+    <t>S-05042</t>
+  </si>
+  <si>
+    <t>S-05043</t>
+  </si>
+  <si>
+    <t>S-05044</t>
+  </si>
+  <si>
+    <t>B02</t>
+  </si>
+  <si>
+    <t>Reno</t>
+  </si>
+  <si>
+    <t>S-05045</t>
+  </si>
+  <si>
+    <t>B04</t>
+  </si>
+  <si>
+    <t>Boise</t>
+  </si>
+  <si>
+    <t>S-05046</t>
+  </si>
+  <si>
+    <t>S-05047</t>
+  </si>
+  <si>
+    <t>B05</t>
+  </si>
+  <si>
+    <t>Fargo</t>
+  </si>
+  <si>
+    <t>S-05048</t>
+  </si>
+  <si>
+    <t>S-05049</t>
+  </si>
+  <si>
+    <t>S-05050</t>
+  </si>
+  <si>
+    <t>S-05051</t>
+  </si>
+  <si>
+    <t>B09</t>
+  </si>
+  <si>
+    <t>Akron</t>
+  </si>
+  <si>
+    <t>S-05052</t>
+  </si>
+  <si>
     <t>Mobile</t>
   </si>
   <si>
-    <t>S-05015</t>
-  </si>
-  <si>
-    <t>B21</t>
-  </si>
-  <si>
-    <t>Dover</t>
-  </si>
-  <si>
-    <t>S-05016</t>
-  </si>
-  <si>
-    <t>B01</t>
-  </si>
-  <si>
-    <t>Tulsa</t>
-  </si>
-  <si>
-    <t>S-05017</t>
-  </si>
-  <si>
-    <t>B15</t>
-  </si>
-  <si>
-    <t>Laredo</t>
-  </si>
-  <si>
-    <t>S-05018</t>
-  </si>
-  <si>
-    <t>B41</t>
-  </si>
-  <si>
-    <t>Hartford</t>
-  </si>
-  <si>
-    <t>S-05019</t>
-  </si>
-  <si>
-    <t>S-05020</t>
-  </si>
-  <si>
-    <t>B07</t>
+    <t>S-05053</t>
+  </si>
+  <si>
+    <t>B43</t>
+  </si>
+  <si>
+    <t>S-05054</t>
+  </si>
+  <si>
+    <t>B23</t>
+  </si>
+  <si>
+    <t>Juneau</t>
+  </si>
+  <si>
+    <t>S-05055</t>
+  </si>
+  <si>
+    <t>S-05056</t>
+  </si>
+  <si>
+    <t>S-05057</t>
+  </si>
+  <si>
+    <t>B16</t>
+  </si>
+  <si>
+    <t>Eugene</t>
+  </si>
+  <si>
+    <t>S-05058</t>
+  </si>
+  <si>
+    <t>B48</t>
+  </si>
+  <si>
+    <t>Norfolk</t>
+  </si>
+  <si>
+    <t>S-05059</t>
+  </si>
+  <si>
+    <t>S-05060</t>
+  </si>
+  <si>
+    <t>B17</t>
+  </si>
+  <si>
+    <t>Spokane</t>
+  </si>
+  <si>
+    <t>S-05061</t>
+  </si>
+  <si>
+    <t>S-05062</t>
+  </si>
+  <si>
+    <t>B37</t>
+  </si>
+  <si>
+    <t>Newark</t>
+  </si>
+  <si>
+    <t>S-05063</t>
+  </si>
+  <si>
+    <t>S-05064</t>
+  </si>
+  <si>
+    <t>B39</t>
+  </si>
+  <si>
+    <t>Richmond</t>
+  </si>
+  <si>
+    <t>S-05065</t>
+  </si>
+  <si>
+    <t>B18</t>
+  </si>
+  <si>
+    <t>Tacoma</t>
+  </si>
+  <si>
+    <t>S-05066</t>
+  </si>
+  <si>
+    <t>S-05067</t>
+  </si>
+  <si>
+    <t>B25</t>
+  </si>
+  <si>
+    <t>S-05068</t>
+  </si>
+  <si>
+    <t>S-05069</t>
+  </si>
+  <si>
+    <t>S-05070</t>
+  </si>
+  <si>
+    <t>S-05071</t>
+  </si>
+  <si>
+    <t>S-05072</t>
+  </si>
+  <si>
+    <t>S-05073</t>
+  </si>
+  <si>
+    <t>S-05074</t>
+  </si>
+  <si>
+    <t>S-05075</t>
+  </si>
+  <si>
+    <t>B13</t>
+  </si>
+  <si>
+    <t>Savannah</t>
+  </si>
+  <si>
+    <t>S-05076</t>
+  </si>
+  <si>
+    <t>B47</t>
+  </si>
+  <si>
+    <t>Durham</t>
+  </si>
+  <si>
+    <t>S-05077</t>
+  </si>
+  <si>
+    <t>B45</t>
+  </si>
+  <si>
+    <t>S-05078</t>
+  </si>
+  <si>
+    <t>S-05079</t>
+  </si>
+  <si>
+    <t>S-05080</t>
+  </si>
+  <si>
+    <t>S-05081</t>
+  </si>
+  <si>
+    <t>S-05082</t>
+  </si>
+  <si>
+    <t>S-05083</t>
+  </si>
+  <si>
+    <t>S-05084</t>
+  </si>
+  <si>
+    <t>S-05085</t>
+  </si>
+  <si>
+    <t>S-05086</t>
+  </si>
+  <si>
+    <t>S-05087</t>
+  </si>
+  <si>
+    <t>S-05088</t>
+  </si>
+  <si>
+    <t>S-05089</t>
+  </si>
+  <si>
+    <t>S-05090</t>
+  </si>
+  <si>
+    <t>S-05091</t>
+  </si>
+  <si>
+    <t>S-05092</t>
+  </si>
+  <si>
+    <t>S-05093</t>
+  </si>
+  <si>
+    <t>S-05094</t>
+  </si>
+  <si>
+    <t>S-05095</t>
+  </si>
+  <si>
+    <t>S-05096</t>
+  </si>
+  <si>
+    <t>S-05097</t>
+  </si>
+  <si>
+    <t>S-05098</t>
+  </si>
+  <si>
+    <t>S-05099</t>
+  </si>
+  <si>
+    <t>S-05100</t>
+  </si>
+  <si>
+    <t>Tucson</t>
+  </si>
+  <si>
+    <t>S-05101</t>
+  </si>
+  <si>
+    <t>S-05102</t>
+  </si>
+  <si>
+    <t>S-05103</t>
+  </si>
+  <si>
+    <t>S-05104</t>
+  </si>
+  <si>
+    <t>S-05105</t>
+  </si>
+  <si>
+    <t>B34</t>
+  </si>
+  <si>
+    <t>S-05106</t>
+  </si>
+  <si>
+    <t>S-05107</t>
+  </si>
+  <si>
+    <t>S-05108</t>
+  </si>
+  <si>
+    <t>S-05109</t>
+  </si>
+  <si>
+    <t>S-05110</t>
+  </si>
+  <si>
+    <t>S-05111</t>
+  </si>
+  <si>
+    <t>S-05112</t>
+  </si>
+  <si>
+    <t>S-05113</t>
+  </si>
+  <si>
+    <t>S-05114</t>
+  </si>
+  <si>
+    <t>S-05115</t>
+  </si>
+  <si>
+    <t>S-05116</t>
+  </si>
+  <si>
+    <t>Toledo</t>
+  </si>
+  <si>
+    <t>S-05117</t>
+  </si>
+  <si>
+    <t>S-05118</t>
+  </si>
+  <si>
+    <t>B24</t>
+  </si>
+  <si>
+    <t>Topeka</t>
+  </si>
+  <si>
+    <t>S-05119</t>
+  </si>
+  <si>
+    <t>S-05120</t>
+  </si>
+  <si>
+    <t>S-05121</t>
+  </si>
+  <si>
+    <t>S-05122</t>
+  </si>
+  <si>
+    <t>S-05123</t>
+  </si>
+  <si>
+    <t>S-05124</t>
+  </si>
+  <si>
+    <t>S-05125</t>
+  </si>
+  <si>
+    <t>S-05126</t>
+  </si>
+  <si>
+    <t>S-05127</t>
+  </si>
+  <si>
+    <t>S-05128</t>
+  </si>
+  <si>
+    <t>S-05129</t>
+  </si>
+  <si>
+    <t>S-05130</t>
+  </si>
+  <si>
+    <t>S-05131</t>
+  </si>
+  <si>
+    <t>S-05132</t>
+  </si>
+  <si>
+    <t>S-05133</t>
+  </si>
+  <si>
+    <t>S-05134</t>
+  </si>
+  <si>
+    <t>Austin</t>
+  </si>
+  <si>
+    <t>S-05135</t>
+  </si>
+  <si>
+    <t>S-05136</t>
+  </si>
+  <si>
+    <t>S-05137</t>
+  </si>
+  <si>
+    <t>S-05138</t>
+  </si>
+  <si>
+    <t>S-05139</t>
+  </si>
+  <si>
+    <t>S-05140</t>
+  </si>
+  <si>
+    <t>S-05141</t>
+  </si>
+  <si>
+    <t>S-05142</t>
+  </si>
+  <si>
+    <t>S-05143</t>
+  </si>
+  <si>
+    <t>S-05144</t>
+  </si>
+  <si>
+    <t>S-05145</t>
+  </si>
+  <si>
+    <t>S-05146</t>
+  </si>
+  <si>
+    <t>S-05147</t>
+  </si>
+  <si>
+    <t>S-05148</t>
+  </si>
+  <si>
+    <t>S-05149</t>
+  </si>
+  <si>
+    <t>S-05150</t>
+  </si>
+  <si>
+    <t>S-05151</t>
+  </si>
+  <si>
+    <t>S-05152</t>
+  </si>
+  <si>
+    <t>S-05153</t>
+  </si>
+  <si>
+    <t>S-05154</t>
+  </si>
+  <si>
+    <t>S-05155</t>
+  </si>
+  <si>
+    <t>S-05156</t>
+  </si>
+  <si>
+    <t>S-05157</t>
+  </si>
+  <si>
+    <t>S-05158</t>
+  </si>
+  <si>
+    <t>S-05159</t>
+  </si>
+  <si>
+    <t>S-05160</t>
+  </si>
+  <si>
+    <t>S-05161</t>
+  </si>
+  <si>
+    <t>S-05162</t>
+  </si>
+  <si>
+    <t>S-05163</t>
+  </si>
+  <si>
+    <t>S-05164</t>
+  </si>
+  <si>
+    <t>S-05165</t>
+  </si>
+  <si>
+    <t>Orlando</t>
+  </si>
+  <si>
+    <t>S-05166</t>
+  </si>
+  <si>
+    <t>S-05167</t>
+  </si>
+  <si>
+    <t>S-05168</t>
+  </si>
+  <si>
+    <t>S-05169</t>
+  </si>
+  <si>
+    <t>Boston</t>
+  </si>
+  <si>
+    <t>S-05170</t>
+  </si>
+  <si>
+    <t>S-05171</t>
+  </si>
+  <si>
+    <t>S-05172</t>
+  </si>
+  <si>
+    <t>S-05173</t>
+  </si>
+  <si>
+    <t>S-05174</t>
+  </si>
+  <si>
+    <t>S-05175</t>
+  </si>
+  <si>
+    <t>S-05176</t>
+  </si>
+  <si>
+    <t>S-05177</t>
+  </si>
+  <si>
+    <t>S-05178</t>
+  </si>
+  <si>
+    <t>S-05179</t>
+  </si>
+  <si>
+    <t>S-05180</t>
+  </si>
+  <si>
+    <t>S-05181</t>
+  </si>
+  <si>
+    <t>S-05182</t>
+  </si>
+  <si>
+    <t>S-05183</t>
+  </si>
+  <si>
+    <t>S-05184</t>
+  </si>
+  <si>
+    <t>B26</t>
+  </si>
+  <si>
+    <t>Denver</t>
+  </si>
+  <si>
+    <t>S-05185</t>
+  </si>
+  <si>
+    <t>S-05186</t>
+  </si>
+  <si>
+    <t>S-05187</t>
+  </si>
+  <si>
+    <t>S-05188</t>
+  </si>
+  <si>
+    <t>S-05189</t>
+  </si>
+  <si>
+    <t>S-05190</t>
+  </si>
+  <si>
+    <t>S-05191</t>
+  </si>
+  <si>
+    <t>S-05192</t>
+  </si>
+  <si>
+    <t>S-05193</t>
+  </si>
+  <si>
+    <t>S-05194</t>
+  </si>
+  <si>
+    <t>S-05195</t>
+  </si>
+  <si>
+    <t>S-05196</t>
+  </si>
+  <si>
+    <t>S-05197</t>
+  </si>
+  <si>
+    <t>S-05198</t>
+  </si>
+  <si>
+    <t>S-05199</t>
+  </si>
+  <si>
+    <t>B03</t>
+  </si>
+  <si>
+    <t>Omaha</t>
+  </si>
+  <si>
+    <t>S-05200</t>
+  </si>
+  <si>
+    <t>S-05201</t>
+  </si>
+  <si>
+    <t>S-05202</t>
+  </si>
+  <si>
+    <t>B40</t>
+  </si>
+  <si>
+    <t>Buffalo</t>
+  </si>
+  <si>
+    <t>S-05203</t>
+  </si>
+  <si>
+    <t>S-05204</t>
+  </si>
+  <si>
+    <t>S-05205</t>
+  </si>
+  <si>
+    <t>S-05206</t>
+  </si>
+  <si>
+    <t>S-05207</t>
+  </si>
+  <si>
+    <t>S-05208</t>
+  </si>
+  <si>
+    <t>S-05209</t>
+  </si>
+  <si>
+    <t>S-05210</t>
+  </si>
+  <si>
+    <t>S-05211</t>
+  </si>
+  <si>
+    <t>S-05212</t>
+  </si>
+  <si>
+    <t>S-05213</t>
+  </si>
+  <si>
+    <t>S-05214</t>
+  </si>
+  <si>
+    <t>S-05215</t>
+  </si>
+  <si>
+    <t>S-05216</t>
+  </si>
+  <si>
+    <t>S-05217</t>
+  </si>
+  <si>
+    <t>S-05218</t>
+  </si>
+  <si>
+    <t>S-05219</t>
+  </si>
+  <si>
+    <t>S-05220</t>
+  </si>
+  <si>
+    <t>S-05221</t>
+  </si>
+  <si>
+    <t>S-05222</t>
+  </si>
+  <si>
+    <t>S-05223</t>
+  </si>
+  <si>
+    <t>S-05224</t>
+  </si>
+  <si>
+    <t>S-05225</t>
+  </si>
+  <si>
+    <t>S-05226</t>
+  </si>
+  <si>
+    <t>S-05227</t>
+  </si>
+  <si>
+    <t>S-05228</t>
+  </si>
+  <si>
+    <t>S-05229</t>
+  </si>
+  <si>
+    <t>S-05230</t>
+  </si>
+  <si>
+    <t>S-05231</t>
+  </si>
+  <si>
+    <t>Oakland</t>
+  </si>
+  <si>
+    <t>S-05232</t>
+  </si>
+  <si>
+    <t>S-05233</t>
+  </si>
+  <si>
+    <t>S-05234</t>
+  </si>
+  <si>
+    <t>S-05235</t>
+  </si>
+  <si>
+    <t>S-05236</t>
+  </si>
+  <si>
+    <t>S-05237</t>
+  </si>
+  <si>
+    <t>S-05238</t>
+  </si>
+  <si>
+    <t>S-05239</t>
+  </si>
+  <si>
+    <t>S-05240</t>
+  </si>
+  <si>
+    <t>S-05241</t>
+  </si>
+  <si>
+    <t>S-05242</t>
+  </si>
+  <si>
+    <t>S-05243</t>
+  </si>
+  <si>
+    <t>S-05244</t>
+  </si>
+  <si>
+    <t>S-05245</t>
+  </si>
+  <si>
+    <t>S-05246</t>
+  </si>
+  <si>
+    <t>S-05247</t>
+  </si>
+  <si>
+    <t>S-05248</t>
+  </si>
+  <si>
+    <t>S-05249</t>
+  </si>
+  <si>
+    <t>S-05250</t>
+  </si>
+  <si>
+    <t>S-05251</t>
+  </si>
+  <si>
+    <t>S-05252</t>
+  </si>
+  <si>
+    <t>S-05253</t>
+  </si>
+  <si>
+    <t>S-05254</t>
+  </si>
+  <si>
+    <t>S-05255</t>
+  </si>
+  <si>
+    <t>S-05256</t>
+  </si>
+  <si>
+    <t>S-05257</t>
   </si>
   <si>
     <t>Salem</t>
-  </si>
-  <si>
-    <t>S-05021</t>
-  </si>
-  <si>
-    <t>B42</t>
-  </si>
-  <si>
-    <t>Wichita</t>
-  </si>
-  <si>
-    <t>S-05022</t>
-  </si>
-  <si>
-    <t>S-05023</t>
-  </si>
-  <si>
-    <t>S-05024</t>
-  </si>
-  <si>
-    <t>B50</t>
-  </si>
-  <si>
-    <t>Irvine</t>
-  </si>
-  <si>
-    <t>S-05025</t>
-  </si>
-  <si>
-    <t>S-05026</t>
-  </si>
-  <si>
-    <t>B38</t>
-  </si>
-  <si>
-    <t>Raleigh</t>
-  </si>
-  <si>
-    <t>S-05027</t>
-  </si>
-  <si>
-    <t>B06</t>
-  </si>
-  <si>
-    <t>Macon</t>
-  </si>
-  <si>
-    <t>S-05028</t>
-  </si>
-  <si>
-    <t>B10</t>
-  </si>
-  <si>
-    <t>Dayton</t>
-  </si>
-  <si>
-    <t>S-05029</t>
-  </si>
-  <si>
-    <t>B31</t>
-  </si>
-  <si>
-    <t>Chicago</t>
-  </si>
-  <si>
-    <t>S-05030</t>
-  </si>
-  <si>
-    <t>B27</t>
-  </si>
-  <si>
-    <t>Miami</t>
-  </si>
-  <si>
-    <t>S-05031</t>
-  </si>
-  <si>
-    <t>S-05032</t>
-  </si>
-  <si>
-    <t>B19</t>
-  </si>
-  <si>
-    <t>Madison</t>
-  </si>
-  <si>
-    <t>S-05033</t>
-  </si>
-  <si>
-    <t>S-05034</t>
-  </si>
-  <si>
-    <t>B29</t>
-  </si>
-  <si>
-    <t>Boston</t>
-  </si>
-  <si>
-    <t>S-05035</t>
-  </si>
-  <si>
-    <t>B35</t>
-  </si>
-  <si>
-    <t>Detroit</t>
-  </si>
-  <si>
-    <t>S-05036</t>
-  </si>
-  <si>
-    <t>S-05037</t>
-  </si>
-  <si>
-    <t>S-05038</t>
-  </si>
-  <si>
-    <t>B46</t>
-  </si>
-  <si>
-    <t>Anaheim</t>
-  </si>
-  <si>
-    <t>S-05039</t>
-  </si>
-  <si>
-    <t>B11</t>
-  </si>
-  <si>
-    <t>Toledo</t>
-  </si>
-  <si>
-    <t>S-05040</t>
-  </si>
-  <si>
-    <t>B12</t>
-  </si>
-  <si>
-    <t>Albany</t>
-  </si>
-  <si>
-    <t>S-05041</t>
-  </si>
-  <si>
-    <t>S-05042</t>
-  </si>
-  <si>
-    <t>S-05043</t>
-  </si>
-  <si>
-    <t>S-05044</t>
-  </si>
-  <si>
-    <t>B02</t>
-  </si>
-  <si>
-    <t>Reno</t>
-  </si>
-  <si>
-    <t>S-05045</t>
-  </si>
-  <si>
-    <t>B04</t>
-  </si>
-  <si>
-    <t>Boise</t>
-  </si>
-  <si>
-    <t>S-05046</t>
-  </si>
-  <si>
-    <t>S-05047</t>
-  </si>
-  <si>
-    <t>B05</t>
-  </si>
-  <si>
-    <t>Fargo</t>
-  </si>
-  <si>
-    <t>S-05048</t>
-  </si>
-  <si>
-    <t>S-05049</t>
-  </si>
-  <si>
-    <t>S-05050</t>
-  </si>
-  <si>
-    <t>S-05051</t>
-  </si>
-  <si>
-    <t>B09</t>
-  </si>
-  <si>
-    <t>Akron</t>
-  </si>
-  <si>
-    <t>S-05052</t>
-  </si>
-  <si>
-    <t>S-05053</t>
-  </si>
-  <si>
-    <t>B43</t>
-  </si>
-  <si>
-    <t>Tucson</t>
-  </si>
-  <si>
-    <t>S-05054</t>
-  </si>
-  <si>
-    <t>B23</t>
-  </si>
-  <si>
-    <t>Juneau</t>
-  </si>
-  <si>
-    <t>S-05055</t>
-  </si>
-  <si>
-    <t>S-05056</t>
-  </si>
-  <si>
-    <t>S-05057</t>
-  </si>
-  <si>
-    <t>B16</t>
-  </si>
-  <si>
-    <t>Eugene</t>
-  </si>
-  <si>
-    <t>S-05058</t>
-  </si>
-  <si>
-    <t>B48</t>
-  </si>
-  <si>
-    <t>Norfolk</t>
-  </si>
-  <si>
-    <t>S-05059</t>
-  </si>
-  <si>
-    <t>S-05060</t>
-  </si>
-  <si>
-    <t>B17</t>
-  </si>
-  <si>
-    <t>Spokane</t>
-  </si>
-  <si>
-    <t>S-05061</t>
-  </si>
-  <si>
-    <t>S-05062</t>
-  </si>
-  <si>
-    <t>B37</t>
-  </si>
-  <si>
-    <t>Newark</t>
-  </si>
-  <si>
-    <t>S-05063</t>
-  </si>
-  <si>
-    <t>S-05064</t>
-  </si>
-  <si>
-    <t>B39</t>
-  </si>
-  <si>
-    <t>Richmond</t>
-  </si>
-  <si>
-    <t>S-05065</t>
-  </si>
-  <si>
-    <t>B18</t>
-  </si>
-  <si>
-    <t>Tacoma</t>
-  </si>
-  <si>
-    <t>S-05066</t>
-  </si>
-  <si>
-    <t>S-05067</t>
-  </si>
-  <si>
-    <t>B25</t>
-  </si>
-  <si>
-    <t>Austin</t>
-  </si>
-  <si>
-    <t>S-05068</t>
-  </si>
-  <si>
-    <t>S-05069</t>
-  </si>
-  <si>
-    <t>S-05070</t>
-  </si>
-  <si>
-    <t>S-05071</t>
-  </si>
-  <si>
-    <t>S-05072</t>
-  </si>
-  <si>
-    <t>S-05073</t>
-  </si>
-  <si>
-    <t>S-05074</t>
-  </si>
-  <si>
-    <t>S-05075</t>
-  </si>
-  <si>
-    <t>B13</t>
-  </si>
-  <si>
-    <t>Savannah</t>
-  </si>
-  <si>
-    <t>S-05076</t>
-  </si>
-  <si>
-    <t>B47</t>
-  </si>
-  <si>
-    <t>Durham</t>
-  </si>
-  <si>
-    <t>S-05077</t>
-  </si>
-  <si>
-    <t>B45</t>
-  </si>
-  <si>
-    <t>Oakland</t>
-  </si>
-  <si>
-    <t>S-05078</t>
-  </si>
-  <si>
-    <t>S-05079</t>
-  </si>
-  <si>
-    <t>S-05080</t>
-  </si>
-  <si>
-    <t>S-05081</t>
-  </si>
-  <si>
-    <t>S-05082</t>
-  </si>
-  <si>
-    <t>S-05083</t>
-  </si>
-  <si>
-    <t>S-05084</t>
-  </si>
-  <si>
-    <t>S-05085</t>
-  </si>
-  <si>
-    <t>S-05086</t>
-  </si>
-  <si>
-    <t>S-05087</t>
-  </si>
-  <si>
-    <t>S-05088</t>
-  </si>
-  <si>
-    <t>S-05089</t>
-  </si>
-  <si>
-    <t>S-05090</t>
-  </si>
-  <si>
-    <t>S-05091</t>
-  </si>
-  <si>
-    <t>S-05092</t>
-  </si>
-  <si>
-    <t>S-05093</t>
-  </si>
-  <si>
-    <t>S-05094</t>
-  </si>
-  <si>
-    <t>S-05095</t>
-  </si>
-  <si>
-    <t>S-05096</t>
-  </si>
-  <si>
-    <t>S-05097</t>
-  </si>
-  <si>
-    <t>S-05098</t>
-  </si>
-  <si>
-    <t>S-05099</t>
-  </si>
-  <si>
-    <t>S-05100</t>
-  </si>
-  <si>
-    <t>S-05101</t>
-  </si>
-  <si>
-    <t>S-05102</t>
-  </si>
-  <si>
-    <t>S-05103</t>
-  </si>
-  <si>
-    <t>S-05104</t>
-  </si>
-  <si>
-    <t>S-05105</t>
-  </si>
-  <si>
-    <t>B34</t>
-  </si>
-  <si>
-    <t>Orlando</t>
-  </si>
-  <si>
-    <t>S-05106</t>
-  </si>
-  <si>
-    <t>S-05107</t>
-  </si>
-  <si>
-    <t>S-05108</t>
-  </si>
-  <si>
-    <t>S-05109</t>
-  </si>
-  <si>
-    <t>S-05110</t>
-  </si>
-  <si>
-    <t>S-05111</t>
-  </si>
-  <si>
-    <t>S-05112</t>
-  </si>
-  <si>
-    <t>S-05113</t>
-  </si>
-  <si>
-    <t>S-05114</t>
-  </si>
-  <si>
-    <t>S-05115</t>
-  </si>
-  <si>
-    <t>S-05116</t>
-  </si>
-  <si>
-    <t>S-05117</t>
-  </si>
-  <si>
-    <t>S-05118</t>
-  </si>
-  <si>
-    <t>B24</t>
-  </si>
-  <si>
-    <t>Topeka</t>
-  </si>
-  <si>
-    <t>S-05119</t>
-  </si>
-  <si>
-    <t>S-05120</t>
-  </si>
-  <si>
-    <t>S-05121</t>
-  </si>
-  <si>
-    <t>S-05122</t>
-  </si>
-  <si>
-    <t>S-05123</t>
-  </si>
-  <si>
-    <t>S-05124</t>
-  </si>
-  <si>
-    <t>S-05125</t>
-  </si>
-  <si>
-    <t>S-05126</t>
-  </si>
-  <si>
-    <t>S-05127</t>
-  </si>
-  <si>
-    <t>S-05128</t>
-  </si>
-  <si>
-    <t>S-05129</t>
-  </si>
-  <si>
-    <t>S-05130</t>
-  </si>
-  <si>
-    <t>S-05131</t>
-  </si>
-  <si>
-    <t>S-05132</t>
-  </si>
-  <si>
-    <t>S-05133</t>
-  </si>
-  <si>
-    <t>S-05134</t>
-  </si>
-  <si>
-    <t>S-05135</t>
-  </si>
-  <si>
-    <t>S-05136</t>
-  </si>
-  <si>
-    <t>S-05137</t>
-  </si>
-  <si>
-    <t>S-05138</t>
-  </si>
-  <si>
-    <t>S-05139</t>
-  </si>
-  <si>
-    <t>S-05140</t>
-  </si>
-  <si>
-    <t>S-05141</t>
-  </si>
-  <si>
-    <t>S-05142</t>
-  </si>
-  <si>
-    <t>S-05143</t>
-  </si>
-  <si>
-    <t>S-05144</t>
-  </si>
-  <si>
-    <t>S-05145</t>
-  </si>
-  <si>
-    <t>S-05146</t>
-  </si>
-  <si>
-    <t>S-05147</t>
-  </si>
-  <si>
-    <t>S-05148</t>
-  </si>
-  <si>
-    <t>S-05149</t>
-  </si>
-  <si>
-    <t>S-05150</t>
-  </si>
-  <si>
-    <t>S-05151</t>
-  </si>
-  <si>
-    <t>S-05152</t>
-  </si>
-  <si>
-    <t>S-05153</t>
-  </si>
-  <si>
-    <t>S-05154</t>
-  </si>
-  <si>
-    <t>S-05155</t>
-  </si>
-  <si>
-    <t>S-05156</t>
-  </si>
-  <si>
-    <t>S-05157</t>
-  </si>
-  <si>
-    <t>S-05158</t>
-  </si>
-  <si>
-    <t>S-05159</t>
-  </si>
-  <si>
-    <t>S-05160</t>
-  </si>
-  <si>
-    <t>S-05161</t>
-  </si>
-  <si>
-    <t>S-05162</t>
-  </si>
-  <si>
-    <t>S-05163</t>
-  </si>
-  <si>
-    <t>S-05164</t>
-  </si>
-  <si>
-    <t>S-05165</t>
-  </si>
-  <si>
-    <t>S-05166</t>
-  </si>
-  <si>
-    <t>S-05167</t>
-  </si>
-  <si>
-    <t>S-05168</t>
-  </si>
-  <si>
-    <t>S-05169</t>
-  </si>
-  <si>
-    <t>S-05170</t>
-  </si>
-  <si>
-    <t>S-05171</t>
-  </si>
-  <si>
-    <t>S-05172</t>
-  </si>
-  <si>
-    <t>S-05173</t>
-  </si>
-  <si>
-    <t>S-05174</t>
-  </si>
-  <si>
-    <t>S-05175</t>
-  </si>
-  <si>
-    <t>S-05176</t>
-  </si>
-  <si>
-    <t>S-05177</t>
-  </si>
-  <si>
-    <t>S-05178</t>
-  </si>
-  <si>
-    <t>S-05179</t>
-  </si>
-  <si>
-    <t>S-05180</t>
-  </si>
-  <si>
-    <t>S-05181</t>
-  </si>
-  <si>
-    <t>S-05182</t>
-  </si>
-  <si>
-    <t>S-05183</t>
-  </si>
-  <si>
-    <t>S-05184</t>
-  </si>
-  <si>
-    <t>B26</t>
-  </si>
-  <si>
-    <t>Denver</t>
-  </si>
-  <si>
-    <t>S-05185</t>
-  </si>
-  <si>
-    <t>S-05186</t>
-  </si>
-  <si>
-    <t>S-05187</t>
-  </si>
-  <si>
-    <t>S-05188</t>
-  </si>
-  <si>
-    <t>S-05189</t>
-  </si>
-  <si>
-    <t>S-05190</t>
-  </si>
-  <si>
-    <t>S-05191</t>
-  </si>
-  <si>
-    <t>S-05192</t>
-  </si>
-  <si>
-    <t>S-05193</t>
-  </si>
-  <si>
-    <t>S-05194</t>
-  </si>
-  <si>
-    <t>S-05195</t>
-  </si>
-  <si>
-    <t>S-05196</t>
-  </si>
-  <si>
-    <t>S-05197</t>
-  </si>
-  <si>
-    <t>S-05198</t>
-  </si>
-  <si>
-    <t>S-05199</t>
-  </si>
-  <si>
-    <t>B03</t>
-  </si>
-  <si>
-    <t>Omaha</t>
-  </si>
-  <si>
-    <t>S-05200</t>
-  </si>
-  <si>
-    <t>S-05201</t>
-  </si>
-  <si>
-    <t>S-05202</t>
-  </si>
-  <si>
-    <t>B40</t>
-  </si>
-  <si>
-    <t>Buffalo</t>
-  </si>
-  <si>
-    <t>S-05203</t>
-  </si>
-  <si>
-    <t>S-05204</t>
-  </si>
-  <si>
-    <t>S-05205</t>
-  </si>
-  <si>
-    <t>S-05206</t>
-  </si>
-  <si>
-    <t>S-05207</t>
-  </si>
-  <si>
-    <t>S-05208</t>
-  </si>
-  <si>
-    <t>S-05209</t>
-  </si>
-  <si>
-    <t>S-05210</t>
-  </si>
-  <si>
-    <t>S-05211</t>
-  </si>
-  <si>
-    <t>S-05212</t>
-  </si>
-  <si>
-    <t>S-05213</t>
-  </si>
-  <si>
-    <t>S-05214</t>
-  </si>
-  <si>
-    <t>S-05215</t>
-  </si>
-  <si>
-    <t>S-05216</t>
-  </si>
-  <si>
-    <t>S-05217</t>
-  </si>
-  <si>
-    <t>S-05218</t>
-  </si>
-  <si>
-    <t>S-05219</t>
-  </si>
-  <si>
-    <t>S-05220</t>
-  </si>
-  <si>
-    <t>S-05221</t>
-  </si>
-  <si>
-    <t>S-05222</t>
-  </si>
-  <si>
-    <t>S-05223</t>
-  </si>
-  <si>
-    <t>S-05224</t>
-  </si>
-  <si>
-    <t>S-05225</t>
-  </si>
-  <si>
-    <t>S-05226</t>
-  </si>
-  <si>
-    <t>S-05227</t>
-  </si>
-  <si>
-    <t>S-05228</t>
-  </si>
-  <si>
-    <t>S-05229</t>
-  </si>
-  <si>
-    <t>S-05230</t>
-  </si>
-  <si>
-    <t>S-05231</t>
-  </si>
-  <si>
-    <t>S-05232</t>
-  </si>
-  <si>
-    <t>S-05233</t>
-  </si>
-  <si>
-    <t>S-05234</t>
-  </si>
-  <si>
-    <t>S-05235</t>
-  </si>
-  <si>
-    <t>S-05236</t>
-  </si>
-  <si>
-    <t>S-05237</t>
-  </si>
-  <si>
-    <t>S-05238</t>
-  </si>
-  <si>
-    <t>S-05239</t>
-  </si>
-  <si>
-    <t>S-05240</t>
-  </si>
-  <si>
-    <t>S-05241</t>
-  </si>
-  <si>
-    <t>S-05242</t>
-  </si>
-  <si>
-    <t>S-05243</t>
-  </si>
-  <si>
-    <t>S-05244</t>
-  </si>
-  <si>
-    <t>S-05245</t>
-  </si>
-  <si>
-    <t>S-05246</t>
-  </si>
-  <si>
-    <t>S-05247</t>
-  </si>
-  <si>
-    <t>S-05248</t>
-  </si>
-  <si>
-    <t>S-05249</t>
-  </si>
-  <si>
-    <t>S-05250</t>
-  </si>
-  <si>
-    <t>S-05251</t>
-  </si>
-  <si>
-    <t>S-05252</t>
-  </si>
-  <si>
-    <t>S-05253</t>
-  </si>
-  <si>
-    <t>S-05254</t>
-  </si>
-  <si>
-    <t>S-05255</t>
-  </si>
-  <si>
-    <t>S-05256</t>
-  </si>
-  <si>
-    <t>S-05257</t>
   </si>
   <si>
     <t>S-05258</t>
@@ -1669,10 +1672,10 @@
         <v>9</v>
       </c>
       <c r="E2" s="2">
-        <v>1101.35</v>
+        <v>1060.9</v>
       </c>
       <c r="F2" s="3">
-        <v>45764</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1689,10 +1692,10 @@
         <v>9</v>
       </c>
       <c r="E3" s="2">
-        <v>513.03</v>
+        <v>895.76</v>
       </c>
       <c r="F3" s="3">
-        <v>45764</v>
+        <v>45752</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1709,10 +1712,10 @@
         <v>16</v>
       </c>
       <c r="E4" s="2">
-        <v>324.23</v>
+        <v>70.44</v>
       </c>
       <c r="F4" s="3">
-        <v>45753</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1726,93 +1729,93 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E5" s="2">
-        <v>70.44</v>
+        <v>670.63</v>
       </c>
       <c r="F5" s="3">
-        <v>45766</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2">
-        <v>1483.16</v>
+        <v>652.49</v>
       </c>
       <c r="F6" s="3">
-        <v>45758</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2">
-        <v>948.97</v>
+        <v>1521.22</v>
       </c>
       <c r="F7" s="3">
-        <v>45772</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2">
-        <v>1015.32</v>
+        <v>513.24</v>
       </c>
       <c r="F8" s="3">
-        <v>45769</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2">
-        <v>1521.22</v>
+        <v>331.98</v>
       </c>
       <c r="F9" s="3">
-        <v>45774</v>
+        <v>45767</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1826,93 +1829,93 @@
         <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2">
-        <v>1075.49</v>
+        <v>178.04</v>
       </c>
       <c r="F10" s="3">
-        <v>45755</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" t="s">
         <v>36</v>
       </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
       <c r="E11" s="2">
-        <v>726.29</v>
+        <v>1020.56</v>
       </c>
       <c r="F11" s="3">
-        <v>45769</v>
+        <v>45775</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2">
-        <v>1231.74</v>
+        <v>1523.62</v>
       </c>
       <c r="F12" s="3">
-        <v>45769</v>
+        <v>45764</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E13" s="2">
-        <v>178.04</v>
+        <v>129.65</v>
       </c>
       <c r="F13" s="3">
-        <v>45774</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E14" s="2">
-        <v>600.72</v>
+        <v>1644.54</v>
       </c>
       <c r="F14" s="3">
-        <v>45763</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1926,13 +1929,13 @@
         <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E15" s="2">
-        <v>877.74</v>
+        <v>297.48</v>
       </c>
       <c r="F15" s="3">
-        <v>45754</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1946,13 +1949,13 @@
         <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E16" s="2">
-        <v>1093.71</v>
+        <v>1391.48</v>
       </c>
       <c r="F16" s="3">
-        <v>45763</v>
+        <v>45756</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1966,13 +1969,13 @@
         <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E17" s="2">
-        <v>129.65</v>
+        <v>1177.77</v>
       </c>
       <c r="F17" s="3">
-        <v>45766</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1986,13 +1989,13 @@
         <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2">
-        <v>838.25</v>
+        <v>124.75</v>
       </c>
       <c r="F18" s="3">
-        <v>45773</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2006,13 +2009,13 @@
         <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E19" s="2">
-        <v>87.06</v>
+        <v>613.47</v>
       </c>
       <c r="F19" s="3">
-        <v>45760</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2026,13 +2029,13 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E20" s="2">
-        <v>693.77</v>
+        <v>1792.81</v>
       </c>
       <c r="F20" s="3">
-        <v>45767</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2043,61 +2046,61 @@
         <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E21" s="2">
-        <v>1391.48</v>
+        <v>1604.26</v>
       </c>
       <c r="F21" s="3">
-        <v>45756</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
         <v>64</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>65</v>
       </c>
-      <c r="C22" t="s">
-        <v>66</v>
-      </c>
       <c r="D22" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2">
-        <v>1435.03</v>
+        <v>1157.55</v>
       </c>
       <c r="F22" s="3">
-        <v>45766</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E23" s="2">
-        <v>917.87</v>
+        <v>1308.57</v>
       </c>
       <c r="F23" s="3">
-        <v>45764</v>
+        <v>45757</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B24" t="s">
         <v>58</v>
@@ -2106,38 +2109,38 @@
         <v>59</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E24" s="2">
-        <v>179.98</v>
+        <v>1055.41</v>
       </c>
       <c r="F24" s="3">
-        <v>45774</v>
+        <v>45756</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" t="s">
         <v>69</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>70</v>
       </c>
-      <c r="C25" t="s">
-        <v>71</v>
-      </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E25" s="2">
-        <v>613.47</v>
+        <v>1143.36</v>
       </c>
       <c r="F25" s="3">
-        <v>45763</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -2146,238 +2149,238 @@
         <v>35</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E26" s="2">
-        <v>1454.28</v>
+        <v>1270.2</v>
       </c>
       <c r="F26" s="3">
-        <v>45775</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" t="s">
         <v>73</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>74</v>
       </c>
-      <c r="C27" t="s">
-        <v>75</v>
-      </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E27" s="2">
-        <v>152.85</v>
+        <v>190.95</v>
       </c>
       <c r="F27" s="3">
-        <v>45767</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" t="s">
         <v>76</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>77</v>
       </c>
-      <c r="C28" t="s">
-        <v>78</v>
-      </c>
       <c r="D28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E28" s="2">
-        <v>1456.09</v>
+        <v>524.47</v>
       </c>
       <c r="F28" s="3">
-        <v>45761</v>
+        <v>45775</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" t="s">
         <v>79</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>80</v>
       </c>
-      <c r="C29" t="s">
-        <v>81</v>
-      </c>
       <c r="D29" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E29" s="2">
-        <v>1157.55</v>
+        <v>39.52</v>
       </c>
       <c r="F29" s="3">
-        <v>45750</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" t="s">
         <v>82</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>83</v>
       </c>
-      <c r="C30" t="s">
-        <v>84</v>
-      </c>
       <c r="D30" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E30" s="2">
-        <v>1615.19</v>
+        <v>1518.51</v>
       </c>
       <c r="F30" s="3">
-        <v>45768</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" t="s">
         <v>85</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>86</v>
       </c>
-      <c r="C31" t="s">
-        <v>87</v>
-      </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E31" s="2">
-        <v>1392.27</v>
+        <v>1194.5</v>
       </c>
       <c r="F31" s="3">
-        <v>45762</v>
+        <v>45764</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B32" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" t="s">
         <v>86</v>
       </c>
-      <c r="C32" t="s">
-        <v>87</v>
-      </c>
       <c r="D32" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E32" s="2">
-        <v>570.95</v>
+        <v>1237.56</v>
       </c>
       <c r="F32" s="3">
-        <v>45762</v>
+        <v>45759</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" t="s">
         <v>89</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>90</v>
       </c>
-      <c r="C33" t="s">
-        <v>91</v>
-      </c>
       <c r="D33" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E33" s="2">
-        <v>1143.36</v>
+        <v>1528.74</v>
       </c>
       <c r="F33" s="3">
-        <v>45758</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B34" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" t="s">
         <v>65</v>
       </c>
-      <c r="C34" t="s">
-        <v>66</v>
-      </c>
       <c r="D34" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E34" s="2">
-        <v>480.44</v>
+        <v>1570.13</v>
       </c>
       <c r="F34" s="3">
-        <v>45767</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" t="s">
         <v>93</v>
       </c>
-      <c r="B35" t="s">
-        <v>94</v>
-      </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E35" s="2">
-        <v>1187</v>
+        <v>54.38</v>
       </c>
       <c r="F35" s="3">
-        <v>45755</v>
+        <v>45759</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" t="s">
         <v>96</v>
       </c>
-      <c r="B36" t="s">
-        <v>97</v>
-      </c>
-      <c r="C36" t="s">
-        <v>98</v>
-      </c>
       <c r="D36" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E36" s="2">
-        <v>1329.66</v>
+        <v>342.01</v>
       </c>
       <c r="F36" s="3">
-        <v>45770</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E37" s="2">
-        <v>524.47</v>
+        <v>66.62</v>
       </c>
       <c r="F37" s="3">
-        <v>45775</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B38" t="s">
         <v>7</v>
@@ -2389,75 +2392,75 @@
         <v>16</v>
       </c>
       <c r="E38" s="2">
-        <v>1578.29</v>
+        <v>1272.81</v>
       </c>
       <c r="F38" s="3">
-        <v>45748</v>
+        <v>45767</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" t="s">
+        <v>100</v>
+      </c>
+      <c r="C39" t="s">
         <v>101</v>
       </c>
-      <c r="B39" t="s">
-        <v>102</v>
-      </c>
-      <c r="C39" t="s">
-        <v>103</v>
-      </c>
       <c r="D39" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E39" s="2">
-        <v>503.94</v>
+        <v>1452.2</v>
       </c>
       <c r="F39" s="3">
-        <v>45749</v>
+        <v>45760</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B40" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C40" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="D40" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E40" s="2">
-        <v>1494.61</v>
+        <v>814.89</v>
       </c>
       <c r="F40" s="3">
-        <v>45764</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C41" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E41" s="2">
-        <v>1194.5</v>
+        <v>1440.95</v>
       </c>
       <c r="F41" s="3">
-        <v>45764</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B42" t="s">
         <v>11</v>
@@ -2466,18 +2469,18 @@
         <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E42" s="2">
-        <v>1496.74</v>
+        <v>969.01</v>
       </c>
       <c r="F42" s="3">
-        <v>45767</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B43" t="s">
         <v>52</v>
@@ -2486,18 +2489,18 @@
         <v>53</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E43" s="2">
-        <v>301.35</v>
+        <v>211.27</v>
       </c>
       <c r="F43" s="3">
-        <v>45767</v>
+        <v>45756</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B44" t="s">
         <v>18</v>
@@ -2506,58 +2509,58 @@
         <v>19</v>
       </c>
       <c r="D44" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E44" s="2">
-        <v>377.48</v>
+        <v>600.64</v>
       </c>
       <c r="F44" s="3">
-        <v>45757</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B45" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E45" s="2">
-        <v>1570.13</v>
+        <v>742.42</v>
       </c>
       <c r="F45" s="3">
-        <v>45763</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C46" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D46" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E46" s="2">
-        <v>1187.84</v>
+        <v>526.6</v>
       </c>
       <c r="F46" s="3">
-        <v>45748</v>
+        <v>45756</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B47" t="s">
         <v>7</v>
@@ -2566,58 +2569,58 @@
         <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E47" s="2">
-        <v>1453.05</v>
+        <v>123.1</v>
       </c>
       <c r="F47" s="3">
-        <v>45749</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C48" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D48" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E48" s="2">
-        <v>1318.04</v>
+        <v>1700.12</v>
       </c>
       <c r="F48" s="3">
-        <v>45761</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B49" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E49" s="2">
-        <v>66.62</v>
+        <v>467.24</v>
       </c>
       <c r="F49" s="3">
-        <v>45750</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B50" t="s">
         <v>11</v>
@@ -2626,138 +2629,138 @@
         <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E50" s="2">
-        <v>708.25</v>
+        <v>274.31</v>
       </c>
       <c r="F50" s="3">
-        <v>45767</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B51" t="s">
+        <v>76</v>
+      </c>
+      <c r="C51" t="s">
         <v>77</v>
       </c>
-      <c r="C51" t="s">
-        <v>78</v>
-      </c>
       <c r="D51" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E51" s="2">
-        <v>540.34</v>
+        <v>1595</v>
       </c>
       <c r="F51" s="3">
-        <v>45753</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B52" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C52" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D52" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E52" s="2">
-        <v>789.78</v>
+        <v>860.15</v>
       </c>
       <c r="F52" s="3">
-        <v>45748</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B53" t="s">
         <v>46</v>
       </c>
       <c r="C53" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="D53" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E53" s="2">
-        <v>814.89</v>
+        <v>1511.06</v>
       </c>
       <c r="F53" s="3">
-        <v>45748</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C54" t="s">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E54" s="2">
-        <v>1512.34</v>
+        <v>467.01</v>
       </c>
       <c r="F54" s="3">
-        <v>45770</v>
+        <v>45752</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B55" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C55" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D55" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E55" s="2">
-        <v>1389.37</v>
+        <v>933.45</v>
       </c>
       <c r="F55" s="3">
-        <v>45774</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B56" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C56" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D56" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E56" s="2">
-        <v>497.95</v>
+        <v>413.27</v>
       </c>
       <c r="F56" s="3">
-        <v>45761</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B57" t="s">
         <v>34</v>
@@ -2766,238 +2769,238 @@
         <v>35</v>
       </c>
       <c r="D57" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E57" s="2">
-        <v>211.27</v>
+        <v>593.04</v>
       </c>
       <c r="F57" s="3">
-        <v>45756</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B58" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C58" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D58" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E58" s="2">
-        <v>1499.38</v>
+        <v>1049.7</v>
       </c>
       <c r="F58" s="3">
-        <v>45757</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B59" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C59" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D59" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E59" s="2">
-        <v>454.78</v>
+        <v>507.37</v>
       </c>
       <c r="F59" s="3">
-        <v>45753</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C60" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="D60" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E60" s="2">
-        <v>470.07</v>
+        <v>1505.54</v>
       </c>
       <c r="F60" s="3">
-        <v>45755</v>
+        <v>45752</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B61" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C61" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D61" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E61" s="2">
-        <v>526.6</v>
+        <v>643.07</v>
       </c>
       <c r="F61" s="3">
-        <v>45756</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B62" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C62" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D62" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E62" s="2">
-        <v>574.43</v>
+        <v>1321.95</v>
       </c>
       <c r="F62" s="3">
-        <v>45749</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B63" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C63" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D63" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E63" s="2">
-        <v>719.49</v>
+        <v>1669.54</v>
       </c>
       <c r="F63" s="3">
-        <v>45758</v>
+        <v>45752</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C64" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D64" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E64" s="2">
-        <v>1639.76</v>
+        <v>535.96</v>
       </c>
       <c r="F64" s="3">
-        <v>45772</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B65" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C65" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D65" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E65" s="2">
-        <v>467.24</v>
+        <v>1005.85</v>
       </c>
       <c r="F65" s="3">
-        <v>45766</v>
+        <v>45772</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B66" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C66" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D66" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E66" s="2">
-        <v>894.99</v>
+        <v>1791.39</v>
       </c>
       <c r="F66" s="3">
-        <v>45751</v>
+        <v>45764</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B67" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C67" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D67" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E67" s="2">
-        <v>447.47</v>
+        <v>1172.72</v>
       </c>
       <c r="F67" s="3">
-        <v>45772</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B68" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C68" t="s">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="D68" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E68" s="2">
-        <v>1312.95</v>
+        <v>1302.96</v>
       </c>
       <c r="F68" s="3">
-        <v>45769</v>
+        <v>45754</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B69" t="s">
         <v>18</v>
@@ -3006,78 +3009,78 @@
         <v>19</v>
       </c>
       <c r="D69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E69" s="2">
-        <v>860.15</v>
+        <v>1167.36</v>
       </c>
       <c r="F69" s="3">
-        <v>45750</v>
+        <v>45759</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B70" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C70" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D70" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E70" s="2">
-        <v>1337.88</v>
+        <v>1352.43</v>
       </c>
       <c r="F70" s="3">
-        <v>45771</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B71" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C71" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E71" s="2">
-        <v>119.89</v>
+        <v>1405.55</v>
       </c>
       <c r="F71" s="3">
-        <v>45775</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B72" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C72" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D72" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E72" s="2">
-        <v>325.9</v>
+        <v>1152.53</v>
       </c>
       <c r="F72" s="3">
-        <v>45761</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B73" t="s">
         <v>14</v>
@@ -3086,18 +3089,18 @@
         <v>15</v>
       </c>
       <c r="D73" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E73" s="2">
-        <v>933.45</v>
+        <v>1505.52</v>
       </c>
       <c r="F73" s="3">
-        <v>45758</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B74" t="s">
         <v>14</v>
@@ -3106,98 +3109,98 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E74" s="2">
-        <v>1267.76</v>
+        <v>1323.54</v>
       </c>
       <c r="F74" s="3">
-        <v>45754</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B75" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C75" t="s">
-        <v>118</v>
+        <v>47</v>
       </c>
       <c r="D75" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E75" s="2">
-        <v>753.01</v>
+        <v>976.27</v>
       </c>
       <c r="F75" s="3">
-        <v>45764</v>
+        <v>45760</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C76" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D76" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E76" s="2">
-        <v>668.94</v>
+        <v>617.75</v>
       </c>
       <c r="F76" s="3">
-        <v>45767</v>
+        <v>45757</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C77" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D77" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E77" s="2">
-        <v>1049.7</v>
+        <v>510.55</v>
       </c>
       <c r="F77" s="3">
-        <v>45758</v>
+        <v>45752</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B78" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C78" t="s">
-        <v>178</v>
+        <v>47</v>
       </c>
       <c r="D78" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E78" s="2">
-        <v>724.76</v>
+        <v>281.72</v>
       </c>
       <c r="F78" s="3">
-        <v>45755</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B79" t="s">
         <v>34</v>
@@ -3206,158 +3209,158 @@
         <v>35</v>
       </c>
       <c r="D79" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E79" s="2">
-        <v>161.13</v>
+        <v>1554.74</v>
       </c>
       <c r="F79" s="3">
-        <v>45749</v>
+        <v>45751</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B80" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C80" t="s">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="D80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E80" s="2">
-        <v>278.99</v>
+        <v>591.05</v>
       </c>
       <c r="F80" s="3">
-        <v>45770</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B81" t="s">
+        <v>69</v>
+      </c>
+      <c r="C81" t="s">
         <v>70</v>
-      </c>
-      <c r="C81" t="s">
-        <v>71</v>
       </c>
       <c r="D81" t="s">
         <v>16</v>
       </c>
       <c r="E81" s="2">
-        <v>643.07</v>
+        <v>932.01</v>
       </c>
       <c r="F81" s="3">
-        <v>45765</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B82" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C82" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D82" t="s">
         <v>9</v>
       </c>
       <c r="E82" s="2">
-        <v>1223.41</v>
+        <v>1211.37</v>
       </c>
       <c r="F82" s="3">
-        <v>45768</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B83" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D83" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E83" s="2">
-        <v>692.68</v>
+        <v>1148.96</v>
       </c>
       <c r="F83" s="3">
-        <v>45763</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B84" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C84" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D84" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E84" s="2">
-        <v>293.24</v>
+        <v>265.41</v>
       </c>
       <c r="F84" s="3">
-        <v>45750</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B85" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C85" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D85" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E85" s="2">
-        <v>535.96</v>
+        <v>1520.16</v>
       </c>
       <c r="F85" s="3">
-        <v>45773</v>
+        <v>45754</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B86" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C86" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="D86" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E86" s="2">
-        <v>204.09</v>
+        <v>500.75</v>
       </c>
       <c r="F86" s="3">
-        <v>45763</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B87" t="s">
         <v>58</v>
@@ -3366,18 +3369,18 @@
         <v>59</v>
       </c>
       <c r="D87" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E87" s="2">
-        <v>594.98</v>
+        <v>608.7</v>
       </c>
       <c r="F87" s="3">
-        <v>45754</v>
+        <v>45772</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B88" t="s">
         <v>58</v>
@@ -3386,290 +3389,290 @@
         <v>59</v>
       </c>
       <c r="D88" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E88" s="2">
-        <v>1092.55</v>
+        <v>483.38</v>
       </c>
       <c r="F88" s="3">
-        <v>45760</v>
+        <v>45761</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B89" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C89" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D89" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E89" s="2">
-        <v>1172.72</v>
+        <v>342.87</v>
       </c>
       <c r="F89" s="3">
-        <v>45750</v>
+        <v>45775</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B90" t="s">
         <v>46</v>
       </c>
       <c r="C90" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="D90" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E90" s="2">
-        <v>1093.97</v>
+        <v>1518.42</v>
       </c>
       <c r="F90" s="3">
-        <v>45768</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B91" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C91" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D91" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E91" s="2">
-        <v>321.81</v>
+        <v>1433.21</v>
       </c>
       <c r="F91" s="3">
-        <v>45748</v>
+        <v>45775</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B92" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C92" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D92" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E92" s="2">
-        <v>769.97</v>
+        <v>755.16</v>
       </c>
       <c r="F92" s="3">
-        <v>45762</v>
+        <v>45767</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B93" t="s">
+        <v>64</v>
+      </c>
+      <c r="C93" t="s">
         <v>65</v>
-      </c>
-      <c r="C93" t="s">
-        <v>66</v>
       </c>
       <c r="D93" t="s">
         <v>9</v>
       </c>
       <c r="E93" s="2">
-        <v>1352.43</v>
+        <v>448.84</v>
       </c>
       <c r="F93" s="3">
-        <v>45768</v>
+        <v>45767</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B94" t="s">
+        <v>76</v>
+      </c>
+      <c r="C94" t="s">
         <v>77</v>
       </c>
-      <c r="C94" t="s">
-        <v>78</v>
-      </c>
       <c r="D94" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E94" s="2">
-        <v>1774.4</v>
+        <v>1461.91</v>
       </c>
       <c r="F94" s="3">
-        <v>45769</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B95" t="s">
+        <v>89</v>
+      </c>
+      <c r="C95" t="s">
         <v>90</v>
       </c>
-      <c r="C95" t="s">
-        <v>91</v>
-      </c>
       <c r="D95" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E95" s="2">
-        <v>789.91</v>
+        <v>1121.28</v>
       </c>
       <c r="F95" s="3">
-        <v>45770</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B96" t="s">
         <v>11</v>
       </c>
       <c r="C96" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="D96" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E96" s="2">
-        <v>520.59</v>
+        <v>1316.84</v>
       </c>
       <c r="F96" s="3">
-        <v>45758</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B97" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C97" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D97" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E97" s="2">
-        <v>1505.52</v>
+        <v>86.33</v>
       </c>
       <c r="F97" s="3">
-        <v>45773</v>
+        <v>45760</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B98" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C98" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D98" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E98" s="2">
-        <v>1356.26</v>
+        <v>713.66</v>
       </c>
       <c r="F98" s="3">
-        <v>45768</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B99" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C99" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D99" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E99" s="2">
-        <v>233.27</v>
+        <v>1178.25</v>
       </c>
       <c r="F99" s="3">
-        <v>45770</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B100" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C100" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D100" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E100" s="2">
-        <v>811.46</v>
+        <v>1613.94</v>
       </c>
       <c r="F100" s="3">
-        <v>45773</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B101" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C101" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
       <c r="D101" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E101" s="2">
-        <v>617.75</v>
+        <v>984.52</v>
       </c>
       <c r="F101" s="3">
-        <v>45757</v>
+        <v>45752</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B102" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C102" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="D102" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E102" s="2">
-        <v>674.22</v>
+        <v>605.17</v>
       </c>
       <c r="F102" s="3">
         <v>45755</v>
@@ -3677,127 +3680,127 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B103" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C103" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D103" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E103" s="2">
-        <v>40.22</v>
+        <v>927.53</v>
       </c>
       <c r="F103" s="3">
-        <v>45771</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B104" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C104" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D104" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E104" s="2">
-        <v>1195.69</v>
+        <v>761.49</v>
       </c>
       <c r="F104" s="3">
-        <v>45763</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B105" t="s">
+        <v>89</v>
+      </c>
+      <c r="C105" t="s">
         <v>90</v>
       </c>
-      <c r="C105" t="s">
-        <v>91</v>
-      </c>
       <c r="D105" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E105" s="2">
-        <v>1554.74</v>
+        <v>1275.12</v>
       </c>
       <c r="F105" s="3">
-        <v>45751</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B106" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C106" t="s">
-        <v>208</v>
+        <v>47</v>
       </c>
       <c r="D106" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E106" s="2">
-        <v>1754.32</v>
+        <v>517.63</v>
       </c>
       <c r="F106" s="3">
-        <v>45756</v>
+        <v>45764</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B107" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C107" t="s">
-        <v>140</v>
+        <v>47</v>
       </c>
       <c r="D107" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E107" s="2">
-        <v>949.23</v>
+        <v>274.22</v>
       </c>
       <c r="F107" s="3">
-        <v>45759</v>
+        <v>45764</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B108" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C108" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="D108" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="E108" s="2">
-        <v>33.41</v>
+        <v>1031.49</v>
       </c>
       <c r="F108" s="3">
-        <v>45761</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B109" t="s">
         <v>49</v>
@@ -3806,18 +3809,18 @@
         <v>50</v>
       </c>
       <c r="D109" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E109" s="2">
-        <v>1211.37</v>
+        <v>1694.04</v>
       </c>
       <c r="F109" s="3">
-        <v>45750</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B110" t="s">
         <v>52</v>
@@ -3826,198 +3829,198 @@
         <v>53</v>
       </c>
       <c r="D110" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E110" s="2">
-        <v>1224.16</v>
+        <v>1688.29</v>
       </c>
       <c r="F110" s="3">
-        <v>45765</v>
+        <v>45761</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B111" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C111" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D111" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E111" s="2">
-        <v>1545.43</v>
+        <v>1088.35</v>
       </c>
       <c r="F111" s="3">
-        <v>45752</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B112" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C112" t="s">
-        <v>109</v>
+        <v>47</v>
       </c>
       <c r="D112" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E112" s="2">
-        <v>670.15</v>
+        <v>606.05</v>
       </c>
       <c r="F112" s="3">
-        <v>45767</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B113" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C113" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D113" t="s">
         <v>9</v>
       </c>
       <c r="E113" s="2">
-        <v>1520.16</v>
+        <v>143.33</v>
       </c>
       <c r="F113" s="3">
-        <v>45754</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B114" t="s">
+        <v>89</v>
+      </c>
+      <c r="C114" t="s">
         <v>90</v>
       </c>
-      <c r="C114" t="s">
-        <v>91</v>
-      </c>
       <c r="D114" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E114" s="2">
-        <v>132.47</v>
+        <v>696.14</v>
       </c>
       <c r="F114" s="3">
-        <v>45755</v>
+        <v>45767</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B115" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C115" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="D115" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E115" s="2">
-        <v>1245.04</v>
+        <v>1686.13</v>
       </c>
       <c r="F115" s="3">
-        <v>45766</v>
+        <v>45757</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B116" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C116" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D116" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E116" s="2">
-        <v>1583</v>
+        <v>677.61</v>
       </c>
       <c r="F116" s="3">
-        <v>45756</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B117" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C117" t="s">
-        <v>106</v>
+        <v>215</v>
       </c>
       <c r="D117" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E117" s="2">
-        <v>483.38</v>
+        <v>1192.25</v>
       </c>
       <c r="F117" s="3">
-        <v>45761</v>
+        <v>45751</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B118" t="s">
+        <v>73</v>
+      </c>
+      <c r="C118" t="s">
         <v>74</v>
       </c>
-      <c r="C118" t="s">
-        <v>75</v>
-      </c>
       <c r="D118" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E118" s="2">
-        <v>1353.4</v>
+        <v>570.82</v>
       </c>
       <c r="F118" s="3">
-        <v>45753</v>
+        <v>45767</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B119" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C119" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D119" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E119" s="2">
-        <v>982.28</v>
+        <v>1162.4</v>
       </c>
       <c r="F119" s="3">
-        <v>45756</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B120" t="s">
         <v>14</v>
@@ -4026,58 +4029,58 @@
         <v>15</v>
       </c>
       <c r="D120" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E120" s="2">
-        <v>377.46</v>
+        <v>962</v>
       </c>
       <c r="F120" s="3">
-        <v>45753</v>
+        <v>45760</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B121" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C121" t="s">
-        <v>172</v>
+        <v>47</v>
       </c>
       <c r="D121" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E121" s="2">
-        <v>1433.21</v>
+        <v>691.55</v>
       </c>
       <c r="F121" s="3">
-        <v>45775</v>
+        <v>45760</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B122" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C122" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D122" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E122" s="2">
-        <v>1260.89</v>
+        <v>1484.27</v>
       </c>
       <c r="F122" s="3">
-        <v>45759</v>
+        <v>45775</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B123" t="s">
         <v>14</v>
@@ -4086,30 +4089,30 @@
         <v>15</v>
       </c>
       <c r="D123" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E123" s="2">
-        <v>1303.41</v>
+        <v>579.15</v>
       </c>
       <c r="F123" s="3">
-        <v>45765</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B124" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C124" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
       <c r="D124" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E124" s="2">
-        <v>1281.9</v>
+        <v>1307.14</v>
       </c>
       <c r="F124" s="3">
         <v>45765</v>
@@ -4117,587 +4120,587 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B125" t="s">
+        <v>85</v>
+      </c>
+      <c r="C125" t="s">
         <v>86</v>
       </c>
-      <c r="C125" t="s">
-        <v>87</v>
-      </c>
       <c r="D125" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E125" s="2">
-        <v>1461.91</v>
+        <v>380.76</v>
       </c>
       <c r="F125" s="3">
-        <v>45755</v>
+        <v>45754</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B126" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C126" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D126" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E126" s="2">
-        <v>259.89</v>
+        <v>513.27</v>
       </c>
       <c r="F126" s="3">
-        <v>45765</v>
+        <v>45752</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B127" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C127" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D127" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E127" s="2">
-        <v>102.68</v>
+        <v>440.13</v>
       </c>
       <c r="F127" s="3">
-        <v>45751</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B128" t="s">
+        <v>69</v>
+      </c>
+      <c r="C128" t="s">
         <v>70</v>
-      </c>
-      <c r="C128" t="s">
-        <v>71</v>
       </c>
       <c r="D128" t="s">
         <v>9</v>
       </c>
       <c r="E128" s="2">
-        <v>1106.62</v>
+        <v>1394.02</v>
       </c>
       <c r="F128" s="3">
-        <v>45754</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B129" t="s">
         <v>14</v>
       </c>
       <c r="C129" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="D129" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E129" s="2">
-        <v>86.33</v>
+        <v>222.48</v>
       </c>
       <c r="F129" s="3">
-        <v>45760</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B130" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C130" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D130" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E130" s="2">
-        <v>475.05</v>
+        <v>472.83</v>
       </c>
       <c r="F130" s="3">
-        <v>45758</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B131" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C131" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D131" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E131" s="2">
-        <v>1350.36</v>
+        <v>1717.98</v>
       </c>
       <c r="F131" s="3">
-        <v>45757</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B132" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C132" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D132" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="E132" s="2">
-        <v>1650.39</v>
+        <v>1547.76</v>
       </c>
       <c r="F132" s="3">
-        <v>45763</v>
+        <v>45772</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B133" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C133" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D133" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E133" s="2">
-        <v>1613.94</v>
+        <v>1746.5</v>
       </c>
       <c r="F133" s="3">
-        <v>45768</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B134" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C134" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D134" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E134" s="2">
-        <v>1526.38</v>
+        <v>1276.06</v>
       </c>
       <c r="F134" s="3">
-        <v>45763</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B135" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C135" t="s">
-        <v>162</v>
+        <v>236</v>
       </c>
       <c r="D135" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E135" s="2">
-        <v>275.63</v>
+        <v>423.15</v>
       </c>
       <c r="F135" s="3">
-        <v>45772</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B136" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C136" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D136" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E136" s="2">
-        <v>473</v>
+        <v>830</v>
       </c>
       <c r="F136" s="3">
-        <v>45755</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B137" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C137" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D137" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E137" s="2">
-        <v>927.53</v>
+        <v>1321.31</v>
       </c>
       <c r="F137" s="3">
-        <v>45773</v>
+        <v>45761</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B138" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C138" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D138" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E138" s="2">
-        <v>657.29</v>
+        <v>330.74</v>
       </c>
       <c r="F138" s="3">
-        <v>45759</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B139" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C139" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D139" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E139" s="2">
-        <v>577.62</v>
+        <v>734.38</v>
       </c>
       <c r="F139" s="3">
-        <v>45761</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B140" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C140" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D140" t="s">
         <v>9</v>
       </c>
       <c r="E140" s="2">
-        <v>354.76</v>
+        <v>1794.9</v>
       </c>
       <c r="F140" s="3">
-        <v>45751</v>
+        <v>45767</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B141" t="s">
+        <v>79</v>
+      </c>
+      <c r="C141" t="s">
         <v>80</v>
       </c>
-      <c r="C141" t="s">
-        <v>81</v>
-      </c>
       <c r="D141" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E141" s="2">
-        <v>517.63</v>
+        <v>1166.58</v>
       </c>
       <c r="F141" s="3">
-        <v>45764</v>
+        <v>45756</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B142" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C142" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D142" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E142" s="2">
-        <v>707.79</v>
+        <v>455.3</v>
       </c>
       <c r="F142" s="3">
-        <v>45751</v>
+        <v>45752</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B143" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C143" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="D143" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E143" s="2">
-        <v>43.17</v>
+        <v>414.72</v>
       </c>
       <c r="F143" s="3">
-        <v>45762</v>
+        <v>45754</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B144" t="s">
+        <v>82</v>
+      </c>
+      <c r="C144" t="s">
         <v>83</v>
       </c>
-      <c r="C144" t="s">
-        <v>84</v>
-      </c>
       <c r="D144" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E144" s="2">
-        <v>1501.95</v>
+        <v>1439.47</v>
       </c>
       <c r="F144" s="3">
-        <v>45766</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B145" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C145" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D145" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E145" s="2">
-        <v>1694.04</v>
+        <v>407.19</v>
       </c>
       <c r="F145" s="3">
-        <v>45771</v>
+        <v>45756</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B146" t="s">
         <v>62</v>
       </c>
       <c r="C146" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D146" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E146" s="2">
-        <v>1345.28</v>
+        <v>907.53</v>
       </c>
       <c r="F146" s="3">
-        <v>45774</v>
+        <v>45752</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B147" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C147" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="D147" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E147" s="2">
-        <v>1331.63</v>
+        <v>67.75</v>
       </c>
       <c r="F147" s="3">
-        <v>45760</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B148" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C148" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D148" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="E148" s="2">
-        <v>1616.3</v>
+        <v>126.22</v>
       </c>
       <c r="F148" s="3">
-        <v>45749</v>
+        <v>45754</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B149" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C149" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D149" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E149" s="2">
-        <v>606.05</v>
+        <v>240.74</v>
       </c>
       <c r="F149" s="3">
-        <v>45758</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B150" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C150" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D150" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E150" s="2">
-        <v>1184.92</v>
+        <v>1532.53</v>
       </c>
       <c r="F150" s="3">
-        <v>45749</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B151" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C151" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D151" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E151" s="2">
-        <v>738.66</v>
+        <v>1001.3</v>
       </c>
       <c r="F151" s="3">
-        <v>45757</v>
+        <v>45772</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B152" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C152" t="s">
-        <v>162</v>
+        <v>236</v>
       </c>
       <c r="D152" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E152" s="2">
-        <v>1255.22</v>
+        <v>1705.49</v>
       </c>
       <c r="F152" s="3">
-        <v>45749</v>
+        <v>45756</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B153" t="s">
         <v>62</v>
       </c>
       <c r="C153" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D153" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E153" s="2">
-        <v>1686.13</v>
+        <v>71.2</v>
       </c>
       <c r="F153" s="3">
-        <v>45757</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B154" t="s">
         <v>58</v>
@@ -4706,18 +4709,18 @@
         <v>59</v>
       </c>
       <c r="D154" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E154" s="2">
-        <v>1132.39</v>
+        <v>454.25</v>
       </c>
       <c r="F154" s="3">
-        <v>45758</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B155" t="s">
         <v>14</v>
@@ -4726,138 +4729,138 @@
         <v>15</v>
       </c>
       <c r="D155" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E155" s="2">
-        <v>1782.24</v>
+        <v>1275.84</v>
       </c>
       <c r="F155" s="3">
-        <v>45757</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B156" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C156" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D156" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E156" s="2">
-        <v>225.31</v>
+        <v>387</v>
       </c>
       <c r="F156" s="3">
-        <v>45754</v>
+        <v>45759</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B157" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C157" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D157" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E157" s="2">
-        <v>570.82</v>
+        <v>1124.32</v>
       </c>
       <c r="F157" s="3">
-        <v>45767</v>
+        <v>45754</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B158" t="s">
+        <v>76</v>
+      </c>
+      <c r="C158" t="s">
         <v>77</v>
       </c>
-      <c r="C158" t="s">
-        <v>78</v>
-      </c>
       <c r="D158" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E158" s="2">
-        <v>554.87</v>
+        <v>379.82</v>
       </c>
       <c r="F158" s="3">
-        <v>45765</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B159" t="s">
+        <v>64</v>
+      </c>
+      <c r="C159" t="s">
         <v>65</v>
       </c>
-      <c r="C159" t="s">
-        <v>66</v>
-      </c>
       <c r="D159" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E159" s="2">
-        <v>394.37</v>
+        <v>997.07</v>
       </c>
       <c r="F159" s="3">
-        <v>45753</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B160" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C160" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D160" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E160" s="2">
-        <v>848.6</v>
+        <v>840.25</v>
       </c>
       <c r="F160" s="3">
-        <v>45748</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B161" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C161" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D161" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E161" s="2">
-        <v>691.55</v>
+        <v>1705.71</v>
       </c>
       <c r="F161" s="3">
-        <v>45760</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B162" t="s">
         <v>58</v>
@@ -4866,98 +4869,98 @@
         <v>59</v>
       </c>
       <c r="D162" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E162" s="2">
-        <v>1213.98</v>
+        <v>876.09</v>
       </c>
       <c r="F162" s="3">
-        <v>45771</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B163" t="s">
+        <v>79</v>
+      </c>
+      <c r="C163" t="s">
         <v>80</v>
       </c>
-      <c r="C163" t="s">
-        <v>81</v>
-      </c>
       <c r="D163" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E163" s="2">
-        <v>493.65</v>
+        <v>164.31</v>
       </c>
       <c r="F163" s="3">
-        <v>45751</v>
+        <v>45767</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B164" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C164" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D164" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E164" s="2">
-        <v>683.2</v>
+        <v>1278.79</v>
       </c>
       <c r="F164" s="3">
-        <v>45774</v>
+        <v>45751</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B165" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C165" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D165" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E165" s="2">
-        <v>1307.14</v>
+        <v>511.21</v>
       </c>
       <c r="F165" s="3">
-        <v>45765</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B166" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C166" t="s">
-        <v>208</v>
+        <v>268</v>
       </c>
       <c r="D166" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E166" s="2">
-        <v>424.7</v>
+        <v>1219.16</v>
       </c>
       <c r="F166" s="3">
-        <v>45753</v>
+        <v>45772</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B167" t="s">
         <v>18</v>
@@ -4966,118 +4969,118 @@
         <v>19</v>
       </c>
       <c r="D167" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E167" s="2">
-        <v>1246.27</v>
+        <v>1770.96</v>
       </c>
       <c r="F167" s="3">
-        <v>45748</v>
+        <v>45752</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B168" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C168" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D168" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E168" s="2">
-        <v>298.53</v>
+        <v>355.76</v>
       </c>
       <c r="F168" s="3">
-        <v>45772</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B169" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C169" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="D169" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E169" s="2">
-        <v>440.13</v>
+        <v>785.22</v>
       </c>
       <c r="F169" s="3">
-        <v>45758</v>
+        <v>45772</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B170" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C170" t="s">
-        <v>95</v>
+        <v>273</v>
       </c>
       <c r="D170" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E170" s="2">
-        <v>1075.91</v>
+        <v>1423.1</v>
       </c>
       <c r="F170" s="3">
-        <v>45769</v>
+        <v>45760</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B171" t="s">
+        <v>85</v>
+      </c>
+      <c r="C171" t="s">
         <v>86</v>
       </c>
-      <c r="C171" t="s">
-        <v>87</v>
-      </c>
       <c r="D171" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="E171" s="2">
-        <v>81.93</v>
+        <v>1039.75</v>
       </c>
       <c r="F171" s="3">
-        <v>45774</v>
+        <v>45764</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B172" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C172" t="s">
-        <v>95</v>
+        <v>273</v>
       </c>
       <c r="D172" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E172" s="2">
-        <v>663.62</v>
+        <v>835.96</v>
       </c>
       <c r="F172" s="3">
-        <v>45754</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B173" t="s">
         <v>55</v>
@@ -5086,18 +5089,18 @@
         <v>56</v>
       </c>
       <c r="D173" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E173" s="2">
-        <v>472.83</v>
+        <v>217.52</v>
       </c>
       <c r="F173" s="3">
-        <v>45771</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B174" t="s">
         <v>49</v>
@@ -5106,18 +5109,18 @@
         <v>50</v>
       </c>
       <c r="D174" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E174" s="2">
-        <v>1222.91</v>
+        <v>682.16</v>
       </c>
       <c r="F174" s="3">
-        <v>45774</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B175" t="s">
         <v>55</v>
@@ -5126,18 +5129,18 @@
         <v>56</v>
       </c>
       <c r="D175" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E175" s="2">
-        <v>1004.84</v>
+        <v>1786.91</v>
       </c>
       <c r="F175" s="3">
-        <v>45766</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B176" t="s">
         <v>55</v>
@@ -5146,38 +5149,38 @@
         <v>56</v>
       </c>
       <c r="D176" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E176" s="2">
-        <v>1546.69</v>
+        <v>698.4</v>
       </c>
       <c r="F176" s="3">
-        <v>45772</v>
+        <v>45767</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B177" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C177" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="D177" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E177" s="2">
-        <v>1746.5</v>
+        <v>1511.5</v>
       </c>
       <c r="F177" s="3">
-        <v>45770</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B178" t="s">
         <v>58</v>
@@ -5186,38 +5189,38 @@
         <v>59</v>
       </c>
       <c r="D178" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E178" s="2">
-        <v>128.59</v>
+        <v>1736.91</v>
       </c>
       <c r="F178" s="3">
-        <v>45767</v>
+        <v>45764</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B179" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C179" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D179" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E179" s="2">
-        <v>862.06</v>
+        <v>1197.34</v>
       </c>
       <c r="F179" s="3">
-        <v>45759</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B180" t="s">
         <v>18</v>
@@ -5226,298 +5229,298 @@
         <v>19</v>
       </c>
       <c r="D180" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E180" s="2">
-        <v>1662.8</v>
+        <v>1212.5</v>
       </c>
       <c r="F180" s="3">
-        <v>45765</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B181" t="s">
+        <v>73</v>
+      </c>
+      <c r="C181" t="s">
         <v>74</v>
       </c>
-      <c r="C181" t="s">
-        <v>75</v>
-      </c>
       <c r="D181" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E181" s="2">
-        <v>830</v>
+        <v>712.51</v>
       </c>
       <c r="F181" s="3">
-        <v>45765</v>
+        <v>45752</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B182" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C182" t="s">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="D182" t="s">
         <v>16</v>
       </c>
       <c r="E182" s="2">
-        <v>1397.13</v>
+        <v>1195.14</v>
       </c>
       <c r="F182" s="3">
-        <v>45768</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B183" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C183" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D183" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E183" s="2">
-        <v>385.25</v>
+        <v>656.37</v>
       </c>
       <c r="F183" s="3">
-        <v>45769</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B184" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C184" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D184" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E184" s="2">
-        <v>1204.26</v>
+        <v>1371.7</v>
       </c>
       <c r="F184" s="3">
-        <v>45761</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
+        <v>288</v>
+      </c>
+      <c r="B185" t="s">
         <v>289</v>
       </c>
-      <c r="B185" t="s">
+      <c r="C185" t="s">
         <v>290</v>
       </c>
-      <c r="C185" t="s">
-        <v>291</v>
-      </c>
       <c r="D185" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E185" s="2">
-        <v>734.38</v>
+        <v>1461.81</v>
       </c>
       <c r="F185" s="3">
-        <v>45753</v>
+        <v>45760</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B186" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C186" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D186" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E186" s="2">
-        <v>1061.21</v>
+        <v>818.5</v>
       </c>
       <c r="F186" s="3">
-        <v>45775</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B187" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C187" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D187" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E187" s="2">
-        <v>1402.04</v>
+        <v>1109.72</v>
       </c>
       <c r="F187" s="3">
-        <v>45763</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B188" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C188" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D188" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E188" s="2">
-        <v>533.61</v>
+        <v>707.49</v>
       </c>
       <c r="F188" s="3">
-        <v>45754</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B189" t="s">
+        <v>64</v>
+      </c>
+      <c r="C189" t="s">
         <v>65</v>
       </c>
-      <c r="C189" t="s">
-        <v>66</v>
-      </c>
       <c r="D189" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E189" s="2">
-        <v>455.3</v>
+        <v>1399.61</v>
       </c>
       <c r="F189" s="3">
-        <v>45752</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B190" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C190" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D190" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E190" s="2">
-        <v>1520.11</v>
+        <v>493.87</v>
       </c>
       <c r="F190" s="3">
-        <v>45754</v>
+        <v>45764</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B191" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C191" t="s">
-        <v>155</v>
+        <v>47</v>
       </c>
       <c r="D191" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E191" s="2">
-        <v>944.62</v>
+        <v>1524.28</v>
       </c>
       <c r="F191" s="3">
-        <v>45756</v>
+        <v>45759</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B192" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C192" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="D192" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E192" s="2">
-        <v>959.95</v>
+        <v>1298.16</v>
       </c>
       <c r="F192" s="3">
-        <v>45772</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B193" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C193" t="s">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="D193" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E193" s="2">
-        <v>407.19</v>
+        <v>100.22</v>
       </c>
       <c r="F193" s="3">
-        <v>45756</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B194" t="s">
+        <v>76</v>
+      </c>
+      <c r="C194" t="s">
         <v>77</v>
       </c>
-      <c r="C194" t="s">
-        <v>78</v>
-      </c>
       <c r="D194" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E194" s="2">
-        <v>159.79</v>
+        <v>306.27</v>
       </c>
       <c r="F194" s="3">
-        <v>45761</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B195" t="s">
         <v>34</v>
@@ -5526,298 +5529,298 @@
         <v>35</v>
       </c>
       <c r="D195" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E195" s="2">
-        <v>173.71</v>
+        <v>889.68</v>
       </c>
       <c r="F195" s="3">
-        <v>45755</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B196" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C196" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D196" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E196" s="2">
-        <v>1001.24</v>
+        <v>1692.63</v>
       </c>
       <c r="F196" s="3">
-        <v>45762</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B197" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C197" t="s">
-        <v>162</v>
+        <v>236</v>
       </c>
       <c r="D197" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E197" s="2">
-        <v>126.22</v>
+        <v>778.21</v>
       </c>
       <c r="F197" s="3">
-        <v>45754</v>
+        <v>45757</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B198" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C198" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D198" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E198" s="2">
-        <v>1479.26</v>
+        <v>846.61</v>
       </c>
       <c r="F198" s="3">
-        <v>45751</v>
+        <v>45756</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B199" t="s">
         <v>46</v>
       </c>
       <c r="C199" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="D199" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E199" s="2">
-        <v>1040</v>
+        <v>1752.02</v>
       </c>
       <c r="F199" s="3">
-        <v>45770</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>305</v>
+      </c>
+      <c r="B200" t="s">
         <v>306</v>
       </c>
-      <c r="B200" t="s">
+      <c r="C200" t="s">
         <v>307</v>
       </c>
-      <c r="C200" t="s">
-        <v>308</v>
-      </c>
       <c r="D200" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E200" s="2">
-        <v>400.17</v>
+        <v>697.53</v>
       </c>
       <c r="F200" s="3">
-        <v>45758</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B201" t="s">
         <v>34</v>
       </c>
       <c r="C201" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D201" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E201" s="2">
-        <v>1001.3</v>
+        <v>403.83</v>
       </c>
       <c r="F201" s="3">
-        <v>45772</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B202" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C202" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D202" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E202" s="2">
-        <v>936.28</v>
+        <v>1114.94</v>
       </c>
       <c r="F202" s="3">
-        <v>45774</v>
+        <v>45775</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
+        <v>310</v>
+      </c>
+      <c r="B203" t="s">
         <v>311</v>
       </c>
-      <c r="B203" t="s">
+      <c r="C203" t="s">
         <v>312</v>
       </c>
-      <c r="C203" t="s">
-        <v>313</v>
-      </c>
       <c r="D203" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E203" s="2">
-        <v>47.93</v>
+        <v>183.5</v>
       </c>
       <c r="F203" s="3">
-        <v>45751</v>
+        <v>45772</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B204" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C204" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D204" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E204" s="2">
-        <v>1467.94</v>
+        <v>1698.39</v>
       </c>
       <c r="F204" s="3">
-        <v>45756</v>
+        <v>45761</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B205" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C205" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D205" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E205" s="2">
-        <v>454.25</v>
+        <v>1493.64</v>
       </c>
       <c r="F205" s="3">
-        <v>45765</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B206" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C206" t="s">
-        <v>95</v>
+        <v>273</v>
       </c>
       <c r="D206" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E206" s="2">
-        <v>704.46</v>
+        <v>946.72</v>
       </c>
       <c r="F206" s="3">
-        <v>45767</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B207" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C207" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D207" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E207" s="2">
-        <v>1196.85</v>
+        <v>1510.31</v>
       </c>
       <c r="F207" s="3">
-        <v>45759</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B208" t="s">
+        <v>64</v>
+      </c>
+      <c r="C208" t="s">
         <v>65</v>
       </c>
-      <c r="C208" t="s">
-        <v>66</v>
-      </c>
       <c r="D208" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E208" s="2">
-        <v>761.88</v>
+        <v>408.56</v>
       </c>
       <c r="F208" s="3">
-        <v>45775</v>
+        <v>45751</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B209" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C209" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D209" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E209" s="2">
-        <v>1124.32</v>
+        <v>396.52</v>
       </c>
       <c r="F209" s="3">
-        <v>45754</v>
+        <v>45751</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B210" t="s">
         <v>58</v>
@@ -5826,318 +5829,318 @@
         <v>59</v>
       </c>
       <c r="D210" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E210" s="2">
-        <v>138.15</v>
+        <v>1671.74</v>
       </c>
       <c r="F210" s="3">
-        <v>45753</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B211" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C211" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D211" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E211" s="2">
-        <v>798.17</v>
+        <v>622.1</v>
       </c>
       <c r="F211" s="3">
-        <v>45775</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B212" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C212" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
       <c r="D212" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="E212" s="2">
-        <v>1412.74</v>
+        <v>1573.72</v>
       </c>
       <c r="F212" s="3">
-        <v>45771</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B213" t="s">
+        <v>85</v>
+      </c>
+      <c r="C213" t="s">
         <v>86</v>
       </c>
-      <c r="C213" t="s">
-        <v>87</v>
-      </c>
       <c r="D213" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E213" s="2">
-        <v>840.25</v>
+        <v>393.82</v>
       </c>
       <c r="F213" s="3">
-        <v>45753</v>
+        <v>45764</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B214" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C214" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D214" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E214" s="2">
-        <v>1213.94</v>
+        <v>957.07</v>
       </c>
       <c r="F214" s="3">
-        <v>45774</v>
+        <v>45752</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B215" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C215" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
       <c r="D215" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E215" s="2">
-        <v>861.4</v>
+        <v>79.11</v>
       </c>
       <c r="F215" s="3">
-        <v>45769</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B216" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C216" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="D216" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E216" s="2">
-        <v>1680.1</v>
+        <v>1084.65</v>
       </c>
       <c r="F216" s="3">
-        <v>45759</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B217" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C217" t="s">
-        <v>95</v>
+        <v>273</v>
       </c>
       <c r="D217" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E217" s="2">
-        <v>164.31</v>
+        <v>197.8</v>
       </c>
       <c r="F217" s="3">
-        <v>45767</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B218" t="s">
         <v>49</v>
       </c>
       <c r="C218" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D218" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="E218" s="2">
-        <v>1405.06</v>
+        <v>1615.76</v>
       </c>
       <c r="F218" s="3">
-        <v>45767</v>
+        <v>45764</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B219" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C219" t="s">
-        <v>162</v>
+        <v>236</v>
       </c>
       <c r="D219" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E219" s="2">
-        <v>1199.17</v>
+        <v>807.81</v>
       </c>
       <c r="F219" s="3">
-        <v>45775</v>
+        <v>45760</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B220" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C220" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="D220" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E220" s="2">
-        <v>1508.69</v>
+        <v>72.27</v>
       </c>
       <c r="F220" s="3">
-        <v>45760</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B221" t="s">
+        <v>73</v>
+      </c>
+      <c r="C221" t="s">
         <v>74</v>
       </c>
-      <c r="C221" t="s">
-        <v>75</v>
-      </c>
       <c r="D221" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E221" s="2">
-        <v>1219.16</v>
+        <v>572.02</v>
       </c>
       <c r="F221" s="3">
-        <v>45772</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B222" t="s">
+        <v>64</v>
+      </c>
+      <c r="C222" t="s">
         <v>65</v>
       </c>
-      <c r="C222" t="s">
-        <v>66</v>
-      </c>
       <c r="D222" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E222" s="2">
-        <v>1423.54</v>
+        <v>179.84</v>
       </c>
       <c r="F222" s="3">
-        <v>45775</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B223" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C223" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D223" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E223" s="2">
-        <v>1193.34</v>
+        <v>1330.53</v>
       </c>
       <c r="F223" s="3">
-        <v>45775</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B224" t="s">
         <v>46</v>
       </c>
       <c r="C224" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="D224" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E224" s="2">
-        <v>684.36</v>
+        <v>498.6</v>
       </c>
       <c r="F224" s="3">
-        <v>45749</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B225" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C225" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="D225" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E225" s="2">
-        <v>785.22</v>
+        <v>156.19</v>
       </c>
       <c r="F225" s="3">
-        <v>45772</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B226" t="s">
         <v>55</v>
@@ -6146,18 +6149,18 @@
         <v>56</v>
       </c>
       <c r="D226" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E226" s="2">
-        <v>669.16</v>
+        <v>1067.7</v>
       </c>
       <c r="F226" s="3">
-        <v>45770</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B227" t="s">
         <v>49</v>
@@ -6166,113 +6169,113 @@
         <v>50</v>
       </c>
       <c r="D227" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E227" s="2">
-        <v>691.78</v>
+        <v>1195.15</v>
       </c>
       <c r="F227" s="3">
-        <v>45765</v>
+        <v>45761</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B228" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C228" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D228" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E228" s="2">
-        <v>1092.61</v>
+        <v>534.91</v>
       </c>
       <c r="F228" s="3">
-        <v>45770</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B229" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C229" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D229" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="E229" s="2">
-        <v>835.96</v>
+        <v>1780.15</v>
       </c>
       <c r="F229" s="3">
-        <v>45753</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B230" t="s">
+        <v>79</v>
+      </c>
+      <c r="C230" t="s">
         <v>80</v>
       </c>
-      <c r="C230" t="s">
-        <v>81</v>
-      </c>
       <c r="D230" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E230" s="2">
-        <v>1490.68</v>
+        <v>1439.96</v>
       </c>
       <c r="F230" s="3">
-        <v>45751</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B231" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C231" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="D231" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E231" s="2">
-        <v>696.44</v>
+        <v>912.16</v>
       </c>
       <c r="F231" s="3">
-        <v>45754</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>341</v>
+      </c>
+      <c r="B232" t="s">
+        <v>173</v>
+      </c>
+      <c r="C232" t="s">
         <v>342</v>
       </c>
-      <c r="B232" t="s">
-        <v>177</v>
-      </c>
-      <c r="C232" t="s">
-        <v>178</v>
-      </c>
       <c r="D232" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E232" s="2">
-        <v>1416.76</v>
+        <v>254.11</v>
       </c>
       <c r="F232" s="3">
-        <v>45753</v>
+        <v>45757</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -6280,19 +6283,19 @@
         <v>343</v>
       </c>
       <c r="B233" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C233" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D233" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E233" s="2">
-        <v>1786.91</v>
+        <v>209.08</v>
       </c>
       <c r="F233" s="3">
-        <v>45758</v>
+        <v>45772</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -6303,16 +6306,16 @@
         <v>58</v>
       </c>
       <c r="C234" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D234" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E234" s="2">
-        <v>1635.81</v>
+        <v>447.21</v>
       </c>
       <c r="F234" s="3">
-        <v>45758</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -6320,19 +6323,19 @@
         <v>345</v>
       </c>
       <c r="B235" t="s">
+        <v>82</v>
+      </c>
+      <c r="C235" t="s">
         <v>83</v>
-      </c>
-      <c r="C235" t="s">
-        <v>84</v>
       </c>
       <c r="D235" t="s">
         <v>9</v>
       </c>
       <c r="E235" s="2">
-        <v>102.07</v>
+        <v>806.98</v>
       </c>
       <c r="F235" s="3">
-        <v>45767</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -6340,19 +6343,19 @@
         <v>346</v>
       </c>
       <c r="B236" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C236" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D236" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E236" s="2">
-        <v>204.75</v>
+        <v>938.57</v>
       </c>
       <c r="F236" s="3">
-        <v>45774</v>
+        <v>45767</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
@@ -6366,13 +6369,13 @@
         <v>35</v>
       </c>
       <c r="D237" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E237" s="2">
-        <v>1736.91</v>
+        <v>763.96</v>
       </c>
       <c r="F237" s="3">
-        <v>45764</v>
+        <v>45756</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -6380,19 +6383,19 @@
         <v>348</v>
       </c>
       <c r="B238" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C238" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D238" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E238" s="2">
-        <v>496.38</v>
+        <v>1779.83</v>
       </c>
       <c r="F238" s="3">
-        <v>45766</v>
+        <v>45764</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -6406,13 +6409,13 @@
         <v>15</v>
       </c>
       <c r="D239" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E239" s="2">
-        <v>1012.88</v>
+        <v>35.41</v>
       </c>
       <c r="F239" s="3">
-        <v>45774</v>
+        <v>45754</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -6420,19 +6423,19 @@
         <v>350</v>
       </c>
       <c r="B240" t="s">
+        <v>289</v>
+      </c>
+      <c r="C240" t="s">
         <v>290</v>
       </c>
-      <c r="C240" t="s">
-        <v>291</v>
-      </c>
       <c r="D240" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E240" s="2">
-        <v>1472.53</v>
+        <v>1731.44</v>
       </c>
       <c r="F240" s="3">
-        <v>45764</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -6440,19 +6443,19 @@
         <v>351</v>
       </c>
       <c r="B241" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C241" t="s">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="D241" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E241" s="2">
-        <v>712.51</v>
+        <v>995.1</v>
       </c>
       <c r="F241" s="3">
-        <v>45752</v>
+        <v>45767</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -6460,19 +6463,19 @@
         <v>352</v>
       </c>
       <c r="B242" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C242" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D242" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E242" s="2">
-        <v>676.51</v>
+        <v>100.53</v>
       </c>
       <c r="F242" s="3">
-        <v>45766</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -6480,19 +6483,19 @@
         <v>353</v>
       </c>
       <c r="B243" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C243" t="s">
-        <v>95</v>
+        <v>273</v>
       </c>
       <c r="D243" t="s">
         <v>16</v>
       </c>
       <c r="E243" s="2">
-        <v>1674.01</v>
+        <v>724.15</v>
       </c>
       <c r="F243" s="3">
-        <v>45763</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -6500,19 +6503,19 @@
         <v>354</v>
       </c>
       <c r="B244" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C244" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D244" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E244" s="2">
-        <v>1649.12</v>
+        <v>821.91</v>
       </c>
       <c r="F244" s="3">
-        <v>45762</v>
+        <v>45760</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -6520,19 +6523,19 @@
         <v>355</v>
       </c>
       <c r="B245" t="s">
+        <v>311</v>
+      </c>
+      <c r="C245" t="s">
         <v>312</v>
       </c>
-      <c r="C245" t="s">
-        <v>313</v>
-      </c>
       <c r="D245" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E245" s="2">
-        <v>1371.7</v>
+        <v>1243.11</v>
       </c>
       <c r="F245" s="3">
-        <v>45758</v>
+        <v>45764</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -6540,19 +6543,19 @@
         <v>356</v>
       </c>
       <c r="B246" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C246" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D246" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E246" s="2">
-        <v>499.83</v>
+        <v>776.41</v>
       </c>
       <c r="F246" s="3">
-        <v>45770</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -6566,13 +6569,13 @@
         <v>15</v>
       </c>
       <c r="D247" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E247" s="2">
-        <v>688.74</v>
+        <v>316.37</v>
       </c>
       <c r="F247" s="3">
-        <v>45763</v>
+        <v>45759</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -6580,19 +6583,19 @@
         <v>358</v>
       </c>
       <c r="B248" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C248" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D248" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E248" s="2">
-        <v>1035.66</v>
+        <v>1382.72</v>
       </c>
       <c r="F248" s="3">
-        <v>45761</v>
+        <v>45756</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -6600,19 +6603,19 @@
         <v>359</v>
       </c>
       <c r="B249" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C249" t="s">
-        <v>208</v>
+        <v>47</v>
       </c>
       <c r="D249" t="s">
         <v>16</v>
       </c>
       <c r="E249" s="2">
-        <v>1109.72</v>
+        <v>1515.38</v>
       </c>
       <c r="F249" s="3">
-        <v>45762</v>
+        <v>45751</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -6620,19 +6623,19 @@
         <v>360</v>
       </c>
       <c r="B250" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C250" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D250" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E250" s="2">
-        <v>448.78</v>
+        <v>1248.35</v>
       </c>
       <c r="F250" s="3">
-        <v>45758</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
@@ -6640,16 +6643,16 @@
         <v>361</v>
       </c>
       <c r="B251" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C251" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D251" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E251" s="2">
-        <v>969.24</v>
+        <v>801.32</v>
       </c>
       <c r="F251" s="3">
         <v>45758</v>
@@ -6660,19 +6663,19 @@
         <v>362</v>
       </c>
       <c r="B252" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C252" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D252" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E252" s="2">
-        <v>1446.92</v>
+        <v>584.51</v>
       </c>
       <c r="F252" s="3">
-        <v>45752</v>
+        <v>45760</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -6680,19 +6683,19 @@
         <v>363</v>
       </c>
       <c r="B253" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C253" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D253" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E253" s="2">
-        <v>493.87</v>
+        <v>238.56</v>
       </c>
       <c r="F253" s="3">
-        <v>45764</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -6700,19 +6703,19 @@
         <v>364</v>
       </c>
       <c r="B254" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C254" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D254" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E254" s="2">
-        <v>511.11</v>
+        <v>610.47</v>
       </c>
       <c r="F254" s="3">
-        <v>45771</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -6720,19 +6723,19 @@
         <v>365</v>
       </c>
       <c r="B255" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C255" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
       <c r="D255" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E255" s="2">
-        <v>282.7</v>
+        <v>219.59</v>
       </c>
       <c r="F255" s="3">
-        <v>45772</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -6746,13 +6749,13 @@
         <v>59</v>
       </c>
       <c r="D256" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E256" s="2">
-        <v>955.84</v>
+        <v>1387.38</v>
       </c>
       <c r="F256" s="3">
-        <v>45751</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -6760,19 +6763,19 @@
         <v>367</v>
       </c>
       <c r="B257" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C257" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D257" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E257" s="2">
-        <v>100.22</v>
+        <v>209.18</v>
       </c>
       <c r="F257" s="3">
-        <v>45762</v>
+        <v>45754</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -6783,181 +6786,181 @@
         <v>62</v>
       </c>
       <c r="C258" t="s">
-        <v>63</v>
+        <v>369</v>
       </c>
       <c r="D258" t="s">
         <v>9</v>
       </c>
       <c r="E258" s="2">
-        <v>993.71</v>
+        <v>1226.43</v>
       </c>
       <c r="F258" s="3">
-        <v>45752</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B259" t="s">
+        <v>85</v>
+      </c>
+      <c r="C259" t="s">
         <v>86</v>
       </c>
-      <c r="C259" t="s">
-        <v>87</v>
-      </c>
       <c r="D259" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E259" s="2">
-        <v>1491.37</v>
+        <v>150.02</v>
       </c>
       <c r="F259" s="3">
-        <v>45757</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B260" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C260" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D260" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E260" s="2">
-        <v>948.07</v>
+        <v>81.63</v>
       </c>
       <c r="F260" s="3">
-        <v>45755</v>
+        <v>45751</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B261" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C261" t="s">
-        <v>172</v>
+        <v>47</v>
       </c>
       <c r="D261" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E261" s="2">
-        <v>1692.63</v>
+        <v>505.32</v>
       </c>
       <c r="F261" s="3">
-        <v>45750</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B262" t="s">
+        <v>79</v>
+      </c>
+      <c r="C262" t="s">
         <v>80</v>
       </c>
-      <c r="C262" t="s">
-        <v>81</v>
-      </c>
       <c r="D262" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E262" s="2">
-        <v>396.47</v>
+        <v>180.12</v>
       </c>
       <c r="F262" s="3">
-        <v>45759</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B263" t="s">
         <v>52</v>
       </c>
       <c r="C263" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D263" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E263" s="2">
-        <v>1312.43</v>
+        <v>1587.15</v>
       </c>
       <c r="F263" s="3">
-        <v>45766</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B264" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C264" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D264" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E264" s="2">
-        <v>571.95</v>
+        <v>668.27</v>
       </c>
       <c r="F264" s="3">
-        <v>45760</v>
+        <v>45754</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B265" t="s">
+        <v>64</v>
+      </c>
+      <c r="C265" t="s">
         <v>65</v>
       </c>
-      <c r="C265" t="s">
-        <v>66</v>
-      </c>
       <c r="D265" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E265" s="2">
-        <v>1752.02</v>
+        <v>135.38</v>
       </c>
       <c r="F265" s="3">
-        <v>45748</v>
+        <v>45754</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B266" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C266" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D266" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="E266" s="2">
-        <v>437.95</v>
+        <v>1653.65</v>
       </c>
       <c r="F266" s="3">
-        <v>45758</v>
+        <v>45759</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B267" t="s">
         <v>55</v>
@@ -6966,158 +6969,158 @@
         <v>56</v>
       </c>
       <c r="D267" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E267" s="2">
-        <v>158.05</v>
+        <v>1485.31</v>
       </c>
       <c r="F267" s="3">
-        <v>45755</v>
+        <v>45764</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B268" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C268" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="D268" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E268" s="2">
-        <v>1672.33</v>
+        <v>1368.93</v>
       </c>
       <c r="F268" s="3">
-        <v>45772</v>
+        <v>45760</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B269" t="s">
+        <v>76</v>
+      </c>
+      <c r="C269" t="s">
         <v>77</v>
-      </c>
-      <c r="C269" t="s">
-        <v>78</v>
       </c>
       <c r="D269" t="s">
         <v>16</v>
       </c>
       <c r="E269" s="2">
-        <v>1114.94</v>
+        <v>290.05</v>
       </c>
       <c r="F269" s="3">
-        <v>45775</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B270" t="s">
+        <v>79</v>
+      </c>
+      <c r="C270" t="s">
         <v>80</v>
       </c>
-      <c r="C270" t="s">
-        <v>81</v>
-      </c>
       <c r="D270" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E270" s="2">
-        <v>1699.39</v>
+        <v>626.93</v>
       </c>
       <c r="F270" s="3">
-        <v>45750</v>
+        <v>45763</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B271" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C271" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D271" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E271" s="2">
-        <v>1750.03</v>
+        <v>519.81</v>
       </c>
       <c r="F271" s="3">
-        <v>45752</v>
+        <v>45761</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B272" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C272" t="s">
-        <v>172</v>
+        <v>47</v>
       </c>
       <c r="D272" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E272" s="2">
-        <v>857.81</v>
+        <v>823.7</v>
       </c>
       <c r="F272" s="3">
-        <v>45764</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B273" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C273" t="s">
-        <v>208</v>
+        <v>268</v>
       </c>
       <c r="D273" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E273" s="2">
-        <v>1493.64</v>
+        <v>1287.64</v>
       </c>
       <c r="F273" s="3">
-        <v>45774</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B274" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C274" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D274" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E274" s="2">
-        <v>170.94</v>
+        <v>1729.05</v>
       </c>
       <c r="F274" s="3">
-        <v>45762</v>
+        <v>45754</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B275" t="s">
         <v>7</v>
@@ -7126,78 +7129,78 @@
         <v>8</v>
       </c>
       <c r="D275" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="E275" s="2">
-        <v>644.34</v>
+        <v>708.37</v>
       </c>
       <c r="F275" s="3">
-        <v>45760</v>
+        <v>45766</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B276" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C276" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D276" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E276" s="2">
-        <v>345.92</v>
+        <v>532.39</v>
       </c>
       <c r="F276" s="3">
-        <v>45757</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B277" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C277" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D277" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E277" s="2">
-        <v>408.56</v>
+        <v>1498.66</v>
       </c>
       <c r="F277" s="3">
-        <v>45751</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B278" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C278" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D278" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E278" s="2">
-        <v>31.05</v>
+        <v>233.78</v>
       </c>
       <c r="F278" s="3">
-        <v>45753</v>
+        <v>45760</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B279" t="s">
         <v>18</v>
@@ -7206,278 +7209,278 @@
         <v>19</v>
       </c>
       <c r="D279" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E279" s="2">
-        <v>1062.72</v>
+        <v>616.81</v>
       </c>
       <c r="F279" s="3">
-        <v>45767</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B280" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C280" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D280" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="E280" s="2">
-        <v>1149.01</v>
+        <v>454.24</v>
       </c>
       <c r="F280" s="3">
-        <v>45767</v>
+        <v>45757</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B281" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C281" t="s">
-        <v>95</v>
+        <v>273</v>
       </c>
       <c r="D281" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E281" s="2">
-        <v>622.1</v>
+        <v>1013.23</v>
       </c>
       <c r="F281" s="3">
-        <v>45768</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B282" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C282" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D282" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E282" s="2">
-        <v>1112.04</v>
+        <v>1724.36</v>
       </c>
       <c r="F282" s="3">
-        <v>45772</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B283" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C283" t="s">
-        <v>208</v>
+        <v>268</v>
       </c>
       <c r="D283" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E283" s="2">
-        <v>917.96</v>
+        <v>228.29</v>
       </c>
       <c r="F283" s="3">
-        <v>45766</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B284" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C284" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D284" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E284" s="2">
-        <v>1059.47</v>
+        <v>252.54</v>
       </c>
       <c r="F284" s="3">
-        <v>45757</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B285" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C285" t="s">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="D285" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E285" s="2">
-        <v>957.07</v>
+        <v>794.53</v>
       </c>
       <c r="F285" s="3">
-        <v>45752</v>
+        <v>45757</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B286" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C286" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D286" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E286" s="2">
-        <v>325.52</v>
+        <v>632.38</v>
       </c>
       <c r="F286" s="3">
-        <v>45748</v>
+        <v>45754</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B287" t="s">
         <v>62</v>
       </c>
       <c r="C287" t="s">
-        <v>63</v>
+        <v>369</v>
       </c>
       <c r="D287" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="E287" s="2">
-        <v>233.82</v>
+        <v>1317.22</v>
       </c>
       <c r="F287" s="3">
-        <v>45769</v>
+        <v>45761</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B288" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C288" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D288" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E288" s="2">
-        <v>1661.52</v>
+        <v>423.78</v>
       </c>
       <c r="F288" s="3">
-        <v>45775</v>
+        <v>45751</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B289" t="s">
         <v>18</v>
       </c>
       <c r="C289" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="D289" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E289" s="2">
-        <v>197.8</v>
+        <v>189.61</v>
       </c>
       <c r="F289" s="3">
-        <v>45766</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B290" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C290" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="D290" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E290" s="2">
-        <v>1018.31</v>
+        <v>1470.05</v>
       </c>
       <c r="F290" s="3">
-        <v>45773</v>
+        <v>45754</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B291" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C291" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D291" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="E291" s="2">
-        <v>763.67</v>
+        <v>517.28</v>
       </c>
       <c r="F291" s="3">
-        <v>45750</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B292" t="s">
+        <v>306</v>
+      </c>
+      <c r="C292" t="s">
         <v>307</v>
       </c>
-      <c r="C292" t="s">
-        <v>308</v>
-      </c>
       <c r="D292" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E292" s="2">
-        <v>835.37</v>
+        <v>1235.28</v>
       </c>
       <c r="F292" s="3">
-        <v>45748</v>
+        <v>45774</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B293" t="s">
         <v>55</v>
@@ -7486,38 +7489,38 @@
         <v>56</v>
       </c>
       <c r="D293" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E293" s="2">
-        <v>72.27</v>
+        <v>1563.27</v>
       </c>
       <c r="F293" s="3">
-        <v>45749</v>
+        <v>45764</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B294" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C294" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D294" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E294" s="2">
-        <v>1582.66</v>
+        <v>204.93</v>
       </c>
       <c r="F294" s="3">
-        <v>45756</v>
+        <v>45767</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B295" t="s">
         <v>46</v>
@@ -7526,18 +7529,18 @@
         <v>47</v>
       </c>
       <c r="D295" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E295" s="2">
-        <v>908.88</v>
+        <v>603.53</v>
       </c>
       <c r="F295" s="3">
-        <v>45772</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B296" t="s">
         <v>34</v>
@@ -7546,18 +7549,18 @@
         <v>35</v>
       </c>
       <c r="D296" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E296" s="2">
-        <v>696.39</v>
+        <v>1039.98</v>
       </c>
       <c r="F296" s="3">
-        <v>45756</v>
+        <v>45773</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B297" t="s">
         <v>18</v>
@@ -7566,93 +7569,93 @@
         <v>19</v>
       </c>
       <c r="D297" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E297" s="2">
-        <v>1330.53</v>
+        <v>801.62</v>
       </c>
       <c r="F297" s="3">
-        <v>45748</v>
+        <v>45765</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B298" t="s">
         <v>58</v>
       </c>
       <c r="C298" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D298" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E298" s="2">
-        <v>261.08</v>
+        <v>617.7</v>
       </c>
       <c r="F298" s="3">
-        <v>45755</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B299" t="s">
         <v>62</v>
       </c>
       <c r="C299" t="s">
-        <v>63</v>
+        <v>369</v>
       </c>
       <c r="D299" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E299" s="2">
-        <v>134.63</v>
+        <v>580.41</v>
       </c>
       <c r="F299" s="3">
-        <v>45762</v>
+        <v>45754</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B300" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C300" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D300" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E300" s="2">
-        <v>701.52</v>
+        <v>34.59</v>
       </c>
       <c r="F300" s="3">
-        <v>45769</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B301" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C301" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="D301" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E301" s="2">
-        <v>1067.7</v>
+        <v>1004.62</v>
       </c>
       <c r="F301" s="3">
-        <v>45748</v>
+        <v>45757</v>
       </c>
     </row>
   </sheetData>
